--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF11D67-B5BA-4846-8D3E-32DE5D21CACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86803C7A-3722-4EBC-B6D7-D70607224449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="3" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="4" activeTab="16" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="797">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -2757,6 +2757,18 @@
   </si>
   <si>
     <t>//flip : 현재 회전값의 반대의 값을 적용한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15. 유료 스프라이트 쉬트 공짜로 쓰는법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인터넷에서 마음에 드는 스프라이트 쉬트를 찾는다. -&gt; 이미지를 캡쳐하고 저장한다 -&gt; 이미지에 있는 워터마크를 제거한다(인터넷에 치면 여러 사이트들이 나옴) -&gt; 이미지 배경을 투명하게 만든다(인터넷에 검색)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그후엔 여타 스프라이트 짜르듯이 똑같이 하면된다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7141,7 +7153,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A320F51B-952E-44A4-8797-50ACF70F49CD}">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -7424,9 +7436,24 @@
         <v>755</v>
       </c>
     </row>
-    <row r="81" spans="11:11" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K81" t="s">
         <v>756</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>796</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86803C7A-3722-4EBC-B6D7-D70607224449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C215254-2789-4884-B49F-468F120D56A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="4" activeTab="16" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="13" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,9 @@
     <sheet name="특별한 자료형(class)" sheetId="12" r:id="rId15"/>
     <sheet name="유니티 editor 사용관련" sheetId="9" r:id="rId16"/>
     <sheet name="유용한 기타 상식" sheetId="5" r:id="rId17"/>
-    <sheet name="UI" sheetId="18" r:id="rId18"/>
-    <sheet name="게임기획" sheetId="15" r:id="rId19"/>
+    <sheet name="긁어온 코드" sheetId="22" r:id="rId18"/>
+    <sheet name="UI" sheetId="18" r:id="rId19"/>
+    <sheet name="게임기획" sheetId="15" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="788">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -2640,135 +2641,77 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(7)주의점 : 유니티 패키지를 쓸때 export할때랑 import할떄 에디터의 버전을 같은버전을 써야 문제나 그런게 안생긴다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5) 등록과 바인딩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-1) 등록 : 특정 스프라이트메쉬에 소속 뼈들의 목록을 정하는게 등록이다. (스프라이트메쉬 게임오브젝트의 인스펙터에서 설정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-2) 바인딩 : 뼈의 애니메이션 동작에 의해서 스프라이트 메쉬가 어떤식으로 동작하는지를 설정해주는것이다. (스프라이트 메쉬 에디터에서 설정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-3) 주의사항 : 등록할떄 같은 이름의 오브젝트가 뜨는경우, 같은이름의 스프라이트메쉬와 뼈대가 섞여있기 때문에 이름을  구분하여 설정 해야한다.(애초에 스프라이트 메쉬나 뼈대를 만들떄 같은이름을 쓰면 안된다)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">등록을 하지않은 뼈대는 바인딩이 불가능하다(바인딩 전에 등록 필수) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스프라이트메쉬의 뼈대를 등록한 이후에는 스프라이트 메쉬의 Transform 컴퍼넌트는 먹통이 된다(위치,로테이션 변경불가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-4)기본적인 바인드 순서 : 등록한 이후에 windows -&gt; anima2d -&gt; spritemesh editor 선택 -&gt;  하이러라키창에서 바인드 할 스프라이트메쉬를 선택 -&gt; 좌측상단에 slice(절점,node)를 선택해서 절점을 위치,개수를 결정 -&gt; slice창에 있는 apply</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-&gt; bind 버튼을 선택한후-&gt; weight툴에서 overlay,pies 선택하고 잘 적용 됬는지 점검한다( pies에서 만약 검정색이 보이면 에러기에 수정해야 한다 보통 auto버튼을 누르거나 slice바를 움직여 가면서 변경) -&gt; bind를 선택한채로 apply(slice apply가 아님)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가중치 툴에서 pies값이 검정색으로 나오면 그부분의 스프라이트메쉬가 사라진다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-5) slice tool : 절점위치와 개수를 설정하는 메뉴(outline detail 항목은 절점의 개수를 늘리거나 줄이는항목이고, alapa cutout은 무시, tessellation 스프라이트 메쉬 내부의 절점 개수를 조절하는 항목이다)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>slice tool로 수동조절해도 결과는 크게 영향을 안미치기 때문에 기본설정대로 써도 큰 지장이 없다 weight tool에서 이상이 있는지만 체크한다(이상없으면 bind apply해서 마무리한다)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-6)weight tool : 뼈대에 의해서 스프라이트메쉬가 얼마나 영향을 받는지 평가하는 툴 (overlay 항목은 스프라이트메쉬에 뼈대가 미치는 영향을 시각적으로 보여주고 pies는 절점에서의 뼈대의 비율값 보여준다(검정은 에러)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>smooth, auto는 자동조정할때 쓰인다)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-7)node(절점)옮기는법 : node를 수정하려면 slice tool을 해제한상태에서 해야한다(slice tool이 켜져있으면 파란색 테투리때문에 못옮긴다),움직일 노드를 선택후 드래그</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-9)노드와 노드사이에 선을 만들고 싶을떄 : 두개의 노드중에서 하나는 클릭, 하나는 shift + 클릭을 하면 두개의 노드가 서로 연결된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-10)노드 weight tool쓸때 주의사항 : 노드를 두개이상잡고 가중치를 설정하면 전체 가중치에 영향이 가므로 주의</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(5-8)노드 추가,삭제하는 방법 : 노드와 노드사이의 선중간에 추가할떄는 shift + 클릭, 내부에서 추가할땐 더블클릭, 노드를 지울떈 지울 노드를 선택후 delete키, 노드 두개를 선택하면 전체선택을 의미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(4-2)애니메이션을 설정할떄 애니메이션을 에니메이션창에서 바로 설정 하지말고, 씬창에서 transform값을 변경하면서 결과값을 본뒤에 적용하면 편하다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(4-3)애니메이션 값 설정할때 주의사항 :  애니메이션 설정할때 버그나서 값이 설정되지 않을땐 애니메이션창을 끄고 다시 키면 된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(6-1)리깅(rigging) : 애니메이션을 위한 뼈대구성법, 리깅의 종류에는 FK(Forward Kinematics), IK(inverse Kinimatics)이 있다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(6-2)FK(Forward kinematics) : 아무 설정도 안하면 나오는 기본값이다. 부모뼈의 종속관계에 의해서 자식뼈의 위치가 자동으로 정해지는 방식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(6-3)IK(Inverse Kinematics) : 특정 조인트(관절)의 포지션을 내가 설정하고싶을때(position만값만 설정가능,rotation와 scale은 설정만되고 적용이 안됨) 사용하는 방식(주로 팔,다리같은 부위에 사용한다),이외에 나머지 특징은 FK와 같다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(6-4)리깅의 우선순위 : 어떤 스프라이트메시의  FK와 IK가 동시에 설정됬을때 IK먼저 적용되고 FK는 적용되지 않는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(6-5) IK 설정법 : </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spritemesh에 적용하는게 아니라 뼈에 적용하는것이다. IK가 적용되야할 뼈가 아니라 그위의 부모뼈를 선택한후 -&gt; 우클릭 -&gt; IK limb 클릭(동그라미의 원점위치가 조인트에 오는지 확인)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(6-6) : Ik Limb 2D 컴퍼넌트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>//orient Child : 체크하면 마지막뼈의 rotation값이 변하지않는다(회전을 막는다)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>//record : 체크하면 매번 애니메이션을 실행할때 연산을 하지않고 미리 계산된 값을 쓴다(게임성능이 좋아진다)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>//flip : 현재 회전값의 반대의 값을 적용한다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15. 유료 스프라이트 쉬트 공짜로 쓰는법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인터넷에서 마음에 드는 스프라이트 쉬트를 찾는다. -&gt; 이미지를 캡쳐하고 저장한다 -&gt; 이미지에 있는 워터마크를 제거한다(인터넷에 치면 여러 사이트들이 나옴) -&gt; 이미지 배경을 투명하게 만든다(인터넷에 검색)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그후엔 여타 스프라이트 짜르듯이 똑같이 하면된다</t>
+    <t>1. 오브젝트 왕복 알고리즘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> [SerializeField] private float moveSpeed;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> private Vector3 startPos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> private Vector3 endPos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> private Vector3 moveDirection;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> void Start()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     startPos = new Vector3(-8f,transform.position.y,transform.position.z);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     endPos = new Vector3(8f,transform.position.y,transform.position.z);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     moveDirection = (endPos - startPos).normalized;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> }</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> void Update()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     // 오브젝트를 endPos 방향으로 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     //MoveTowards 메소드의 정의 : 첫번째 매개변수는 시작점, 두번째 매개변수가 방향,세번째 매개변수 호출될때 마다의 이동량</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     transform.position = Vector3.MoveTowards(transform.position, endPos, moveSpeed * Time.deltaTime);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     //첫번째와 두번째 매개변수 사이의 절댓값 거리가 0.001f 보다 작다면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     if (Vector3.Distance(transform.position, endPos) &lt; 0.001f)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         // startPos와 endPos를 서로 바꿈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Vector3 temp = startPos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         startPos = endPos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         endPos = temp;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. vector 형 메소드나 프로퍼티를 쓸때 주의할 점 : vector형식으로 설정할때 x,y 성분을 따로 따로 설정 할 수 없다 그러므로 이동방식을 velocity를 활용한 경우엔 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2883,138 +2826,6 @@
         <a:xfrm>
           <a:off x="7620" y="11049000"/>
           <a:ext cx="1809524" cy="504762"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>8561</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>214045</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>548574</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>131706</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74CF5A24-698E-65B7-7D8D-01F40B5C92A1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8561" y="15351303"/>
-          <a:ext cx="5214755" cy="3256762"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>17125</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>17124</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>417685</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>205483</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7AED40E-33A5-B126-1059-EA0907BAA214}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17125" y="22055191"/>
-          <a:ext cx="2404021" cy="1969213"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>17124</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>335936</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>150556</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33C57319-F484-97B3-01E5-84CE362EDE39}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="24281259"/>
-          <a:ext cx="4342857" cy="1914286"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3668,13 +3479,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>7621</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>151971</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4937,7 +4748,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83395862-6542-455B-8080-4B1FD46BA113}">
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -5005,33 +4816,33 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
         <v>488</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
         <v>490</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7153,7 +6964,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A320F51B-952E-44A4-8797-50ACF70F49CD}">
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -7251,209 +7062,189 @@
         <v>537</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>764</v>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
         <v>259</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A56" t="s">
         <v>260</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
         <v>306</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
         <v>420</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A67" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A71" t="s">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="K75" t="s">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K74" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="K81" t="s">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K80" t="s">
         <v>756</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A90" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A91" t="s">
-        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -7464,6 +7255,142 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BB7779-1044-4C8F-BB0E-ACC6D5920DCD}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>774</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A67CEF4-BE01-4763-BDC6-975F09EE47AA}">
   <dimension ref="A1:H59"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -7637,72 +7564,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0A0146-AD32-4B49-937B-CB2E2BCDD816}">
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>455</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -7787,9 +7648,75 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0A0146-AD32-4B49-937B-CB2E2BCDD816}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>455</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C603B226-F442-4FB1-BB22-955D26865001}">
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -8070,6 +7997,11 @@
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>787</v>
       </c>
     </row>
   </sheetData>
@@ -8080,7 +8012,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077E7B44-DC3A-4864-9EC7-4ADF55F1E293}">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -8323,270 +8255,31 @@
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>782</v>
+        <v>745</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>783</v>
+        <v>746</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A63" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A65" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A66" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A67" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A70" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A71" s="1" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A72" s="1" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A73" s="1" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A74" s="1" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A75" s="1" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A76" s="1"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A77" s="1"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A78" s="1"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A79" s="1"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A80" s="1"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A81" s="1"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A82" s="1"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A83" s="1"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A85" s="1"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A86" s="1"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A87" s="1"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A88" s="1"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A89" s="1"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A91" s="1" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A92" s="1" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A93" s="1" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A94" s="1"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A95" s="1" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A96" s="1" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A97" s="1" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A98" s="1" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A99" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="C99" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A100" s="1"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A101" s="1"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A102" s="1"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A103" s="1"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A104" s="1"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A105" s="1"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A106" s="1"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A107" s="1"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A108" s="1"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A109" s="1" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A110" s="1"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A111" s="1"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A112" s="1"/>
-      <c r="H112" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A113" s="1"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A114" s="1"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A115" s="1"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A116" s="1"/>
-      <c r="H116" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A117" s="1"/>
-      <c r="H117" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A122" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A124" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A126" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A127" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A128" t="s">
         <v>753</v>
       </c>
     </row>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\컴퓨터 노하우\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CD2E1B-82B2-414B-8A78-71B777FC969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252BD0EF-9769-4B80-AFEF-6A02717182BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="2" activeTab="10" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="1" activeTab="14" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="543">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -1187,10 +1187,6 @@
     <t>(5)스프라이트 가져와서 사용할때, 메타파일이 있다면 같이가져와야 자르는 작업을 편하게 할 수 있다(메타파일안에 자르기정보도 같이 포함되있기 때문이다)</t>
   </si>
   <si>
-    <t>1.spirt sheet 쪼개기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(1)유니티에서 Scene에 마이크 역할을 한다.</t>
   </si>
   <si>
@@ -1332,449 +1328,475 @@
     <t>(2)만드는법 : 하이러라키창에 있는 오브젝트를 프로젝트창에 옮긴후 -&gt; 코드에서 작성 -&gt; 퍼블릭 필드에 프로젝트로 옮긴 오브젝트를 연결해준다.</t>
   </si>
   <si>
+    <t xml:space="preserve">        float span = 1.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        float delta = 0;</t>
+  </si>
+  <si>
+    <t>private void Update() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        delta += Time.deltaTime;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if(DeltaSpeed &gt; span)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            DeltaSpeed = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            GameObject go = Instantiate(spike);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            go.transform.position = new Vector3(px,7,0);</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.collision.contact[] </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15. Prefabs(프리팹 복제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)주의사항 : 2D프로젝트에서는 콜백안됨.</t>
+  </si>
+  <si>
+    <t>(2)2D프로젝트에선 2D형 컴퍼넌트,메소드를 사용할것 예외는 vector3</t>
+  </si>
+  <si>
+    <t>2.OnCollisionEnter()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)SortingLayer로 정렬하기 : Sprite Renderer 컴퍼넌트 -&gt; Sorting Layer -&gt; Add Sorting Layer -&gt; +버튼클릭 -&gt; Layer추가(숫자가 높을수록 앞에 있고 낮을수록 가려진다) -&gt;각 오브젝트 선택후Sorting Layer값선택</t>
+  </si>
+  <si>
+    <t>11.레이어로 정렬하기(오브젝트들이 화면에 겹쳐지는 순서)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)오브젝트 크기구하는 방법 : 콜라이더를 씌워본다. -&gt; 콜라이더의 사이즈값을 체크한다 ex) 사각형오브젝트에 박스콜라이더를 씌워서 사이즈 체크</t>
+  </si>
+  <si>
+    <t>2.배경이어붙이기(Crankie Box)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)메인 카메라 -&gt; background -&gt; 스포이드 눌러서 배경색 찍기</t>
+  </si>
+  <si>
+    <t>12.메인카메라 배경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)stackoverflow</t>
+  </si>
+  <si>
+    <t>(2)github</t>
+  </si>
+  <si>
+    <t>11.개발자가 알아야하는 사이트 목록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)Canvas 오브젝트 선택 -&gt; 인스펙터창에서 Canvas Scaler 컴퍼넌트의 UI Scale Mode를 scale with screen size 선택 -&gt; 내가 설치하려는 디바이스 해상도를 입력(비율로 적어도 OK) </t>
+  </si>
+  <si>
+    <t>(2)UI Scale Mode를 Constant Pixel Size로 선택하면 유니티에디터에서 보이는대로 안보일 확률이 크다 따라서 scale with sreen size를 선택해야 한다.(가장 선호도높은 디바이스를 찾은뒤 걔를 기준으로 UI를 구성한다)</t>
+  </si>
+  <si>
+    <t>1. 유니티 에디터에서 보이는대로 실제 디바이스에서 UI가 보이게 하는 방법(유니티에디터에서는 실제디바이스에서 보이는거랑 다를 수 있다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)모니터 픽셀 하나하나에 컬러값(RGBA A는 투명도)을 구하는 연산순서를 정의한것 따라서 이순서에 맞춰 연산을 해야된다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">예 )60Hz짜리 해상도 1920X1080 모니터의 경우 픽셀이 약 207만개, 60분의 1초마다 207만개의 픽셀의 컬러값을 계산해야 한다. 이계산과정은 GPU에서 수행한다. </t>
+  </si>
+  <si>
+    <t>예) 고성능 게임의 경우(조명환경이 복잡하거나 시시각각으로 환경이 변하는 경우) 각픽셀에 컬러값을 계산하는데 굉장히 많은 연산작업이 필요하게 된다. 따라서 모니터 주파수 60분의 1초마다 출력해야하는데</t>
+  </si>
+  <si>
+    <t>그걸 처리못해 버벅거리는 현상이 버퍼링 현상이다.</t>
+  </si>
+  <si>
+    <t>1. 렌더링 파이프라인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)기본적으로 scale with size모드를 사용해야 하며, 해상도 비율이 다른 디바이스에 대응하기 위해 UI 요소들으 배치가 가로방향 위주이면 Match값을 width &gt; height로 구성해주고, 세로방향 위주이면</t>
+  </si>
+  <si>
+    <t>Match값을 width &lt; height로 구성해준ㄴ다. 동일한 해상도 비율의 디바이스 간에는 Match값이 의미가 없음 Match값은 유니티 에디터에서 기준으로 삼은 해상도 비율과 다른 디바이스에 해당 앱이</t>
+  </si>
+  <si>
+    <t>설치되었을때 UI의 배치가 어떤식으로 조정할것인지에 대한 factor(어떤요인이 되는 변수)값임 따라서, 유니티 에디터에서 기준으로 삼은 해상도 비율과 일치하는 디바이스에서는 Match값은 의미가 없다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.Canvas 옵션설정 방법 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)메모리상에 오직 인스턴스가 하나만 존재해야 하는 클래스 (예를들면 장치의 부품들처럼 하나만 존재하는 부품을 소스코드에서 가져다 사용해야 될 경우 그부품 클래스의 인스턴스가 여러개 존재하는것은 모순이다.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)만드는 방법 : 생성자를 private으로 만든다( private Store() { } ) -&gt; static 필드로 객체 생성(  private static   Store instance = new Store(); ) </t>
+  </si>
+  <si>
+    <t>-&gt; 객체의 getter 구현( public static Store getInstance() {return instance}</t>
+  </si>
+  <si>
+    <t>(3)유니티에서 싱글톤 만드는법 :</t>
+  </si>
+  <si>
+    <t>16.싱글톤(single tone)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)추상클래스는 추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)를 가지고있는 클래스</t>
+  </si>
+  <si>
+    <t>(2)추상클래스를 상속한 자식클래스에서 그 추상메소드를 오버라이딩해서 추상메소드를 사용할 수 있는 메소드로 만든다.(구현) extends사용</t>
+  </si>
+  <si>
+    <t>(3)단,  자식클래스에서 추상클래스의 추상메소드를 오버라이딩 할 의무는 없다(선택이다  extends 사용)</t>
+  </si>
+  <si>
+    <t>(1)상수,추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)만 가지고있는 클래스 필드,일반메소드는 존재할 수 없음.</t>
+  </si>
+  <si>
+    <t>(2)자식인터페이스에서 상속 가능(extends) 자식인터페이스끼리 상속</t>
+  </si>
+  <si>
+    <t>(3)자식클래스에서 상속하는경우 반드시 추상클래스의 추상메소드를 의무적으로 구현해줘야함(implements 사용)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)추상클래스와의 차이점 : 추상메소드의 구현을 자식클래스에서 강제적으로 하면 인터페이스, 선택이면 추상클래스 이다. 그리고 추상클래스와 인터페이스는 공통적으로 다형성(오버라이딩,오버로딩) 구현의 수단이다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">다만 인터페이스가 추상클래스보다 더 강제성을 띈다. </t>
+  </si>
+  <si>
+    <t>(1)사용법 : 참조변수.GetHashCode()</t>
+  </si>
+  <si>
+    <t>17.추상 클래스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.인터페이스(interface)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.인스턴트의 주소값을 알려주는 메소드(GetHashCode())</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 게임시작시 필요한 오브젝트를 미리 만들어서 특정영역(게임화면 밖)에 배치해두고 필요할때마다 갖다쓰고 다쓰면 원래위치로 반환 게임실행중에 해당오브젝트가 새로 생성되거나 삭제되지 않는다.</t>
+  </si>
+  <si>
+    <t>(2)프리팹공장 방식과의 차이점 : 오브젝트를 미리만들지않고 게임실행중에 필요할때마다 Instantiate()를 사용해서 복제하고 필요없으면 Destroy()메소드로 삭제한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)장단점 : 장점은 게임실행중에 삭제(가비지 컬렉션)작업이 없기 때문에 쾌적하다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">단점 : 게임시작시에 오브젝트를 만드는데 로딩시간이 필요하다.(프리팹공장방식에선 Destroy()메소드를 호출하여 삭제하는것이 실질적으로는 가비지컬렉션 작업이 발생하는것 이며 가비지컬렉션은 </t>
+  </si>
+  <si>
+    <t>메인쓰레드(어떤 주작업영역(UI나 핵심적인 작업등)상에서 작업처리가 되기 때문에 게임이 중지된다. 사용자가 느끼기에 버퍼링이 생기는것 처럼 느끼게 된다.)</t>
+  </si>
+  <si>
+    <t>3.오브젝트 풀링(object pooling)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)특징 : 배열인데도 배열명이 상수가 아니라 참조변수이다.</t>
+  </si>
+  <si>
+    <t>(2)만드는법 : GameObject[] platforms = new GameObject[count]; // new연산자를 사용한다. 즉 우항의 배열공간이 heap영역에 생긴다. 그리고 그것뿐만이 아니라 결론적으로 클래스 인스턴스 처럼 생긴다. 그안에 배열데이터가 들어간다</t>
+  </si>
+  <si>
+    <t>20. c#에서의 배열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LLVM ERROR: IO failure on output stream: No space left on device</t>
+  </si>
+  <si>
+    <t>PLEASE submit a bug report to https://github.com/android-ndk/ndk/issues and include the crash backtrace.</t>
+  </si>
+  <si>
+    <t>Stack dump:</t>
+  </si>
+  <si>
+    <t>Program arguments: "C:/Program Files/Unity/Hub/Editor/2022.3.17f1/Editor/Data/PlaybackEngines/AndroidPlayer/NDK/toolchains/llvm/prebuilt/windows-x86_64/bin/llvm-objcopy.exe" --only-keep-debug Library/Bee/artifacts/Android/libunity/armeabi-v7a/unstripped/libunity.so Library/Bee/artifacts/Android/libunity/armeabi-v7a/libunity.dbg.so</t>
+  </si>
+  <si>
+    <t>UnityEngine.GUIUtility:ProcessEvent (int,intptr,bool&amp;)</t>
+  </si>
+  <si>
+    <t>(1)원인 : 하드용량 부족</t>
+  </si>
+  <si>
+    <t>(2)대처법 : 이런 에러싸인이 나오면 pc의 하드용량이 모자란지 확인해본다. 하드용량을 충분히 잡아준뒤 다시 빌드한다.</t>
+  </si>
+  <si>
+    <t>(1)원인 : 같은 프로젝트안에 동명의 Camera 스크립트가 존재 하기때문(Camera.mainScreenToWorldPoint(Input.mousePosition); 이 메소드를 호출할때 유니티에서 제공하는 Camera클래스와 이름이 같기때문에 에러가 발생)</t>
+  </si>
+  <si>
+    <t>(2)대처법 : 유니티 라이브러리에서 제공하는 클래스이름과 같은 이름으로 스크립트를 만들지 않는다.(좋은이름 짓는 방법 : 지으려는 이름에 _자기이름을 같이 사용한다거나 해서 겹치지않게 한다.)</t>
+  </si>
+  <si>
+    <t>6.Building Library\Bee\artifacts\Android\libunity\armeabi-v7a\libunity.dbg.so failed with output:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6-1 Assets\Script\slingShotScript.cs(32,50): error CS0117: 'Camera' does not contain a definition for 'main'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 매개변수로 설정한 디바이스상(스크린좌표계,픽셀단위를 사용)의 좌표를 유니티의 월드좌표계(유니티 자체 단위계(눈금))로 변환해준다 단, Z값은 카메라의 Z값으로 반환 즉 카메라랑 선상에 있어서 안보인다</t>
+  </si>
+  <si>
+    <t>(2)대처법 : 2D일때는 vector2로 명시적형변환을 해준다.</t>
+  </si>
+  <si>
+    <t>(2-1) 예시 스크립트 : transform.position = (Vector2)Camera.main.ScreenToWorldPoint(Input.mousePosition);</t>
+  </si>
+  <si>
+    <t>7. Camera.main.ScreenToWorldPoint();</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 :  오브젝트의 궤적(발자취)을 그려주는 컴퍼넌트</t>
+  </si>
+  <si>
+    <t>(2)사용법</t>
+  </si>
+  <si>
+    <t>(2-1) Materials : 설정안하면 기본값으로 보라색 색종이(사각형)으로 나옴 머터리얼을 다른값으로 설정하면 머터리얼대로 나옴 단, 레이어 정렬이 적용되는것과 안되는것이 있음 적용되는것은 파티클만 가능</t>
+  </si>
+  <si>
+    <t>1.Trail Renderer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)setActive는 GameObject클래스 소속의 메소드고 GameObject클래스 + 상속한 자식클래스의 참조변수에서만 사용할 수 있다. 따라서 GameObject와 상속관계가 없는 Component형 참조변수(예 : TraillRenderer)를 통해서는 호출 할 수 없다</t>
+  </si>
+  <si>
+    <t>(2)따라서 Component형 참조변수를 활성화시키거나 비활성화 시킬때는 SetActive를 사용할 수 없고, Component클래스에서 제공하는 enabled 프로퍼티를 사용해서 활성화,비활성화 처리를 할 수있다.</t>
+  </si>
+  <si>
+    <t>16. setActive와 Enabled의 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)동기식(sync) : 동기식은 메소드가 호출되면 메소드가 실행종료될때까지 다음라인으로 안넘어가고 대기상태</t>
+  </si>
+  <si>
+    <t>(2)비동기식(async) : 비동기식은 메소드호출되고 메소드의 종료 여분상관없이 다음라인으로 넘어감 (예시: StartCoroutine)</t>
+  </si>
+  <si>
+    <t>21.메소드의 동작방식(동기식,비동기식)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)GameObject클래스와 아무런 상속관계가 없다. 따라서 서로간에 형변환이 불가능하다. </t>
+  </si>
+  <si>
+    <t>(2)하지만 Unity에서는 Scene에 추가된 모든자로형은 GameObject형으로도 취급되므로 형변환이 가능하다. UNITY에서만 해당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.UI 자료형(예 : Slider) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)힘의 공식 : F = ma // f는 힘,m은 질량, a는 가속도 </t>
+  </si>
+  <si>
+    <t>(1)E = mc^2 // E는 에너지,m는 질량,c는 광속도</t>
+  </si>
+  <si>
+    <t>(1) 하는법 :</t>
+  </si>
+  <si>
+    <t>3.뉴턴의 운동방정식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.Rigidbody 컴퍼넌트 질량값 조절</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.아인슈타인의 에너지 공식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) if(!(collision.gameObject.tag.Equals("Ground"))) //코드의 맨앞부분에 적는다 햇갈린다면 ()를 사용해서 명시적으로 구분을 해줄것</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            x.SetTrigger("New Trigger");</t>
+  </si>
+  <si>
+    <t>22. !(not) 붙이는위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)일단 필요한 자료형 이름을 소스코드에 적는다(using이 안되있다면 빨간줄이 그어진다)</t>
+  </si>
+  <si>
+    <t>(2)빨간줄 그어지고 빨간색 X아이콘이 나타나고 그걸 클릭한다</t>
+  </si>
+  <si>
+    <t>(3)목록으로 오류사항을 해결할수 있는 해결책을 제시해준다 그중에서 선택한다.</t>
+  </si>
+  <si>
+    <t>1.자료형의 namespace가 기억안날때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)https://jinhyo98.tistory.com/436 참고</t>
+  </si>
+  <si>
+    <t>12.폴더내 특정 키워드를 가진 파일찾기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)게임오브젝트 : 유니티 내에서 사용하는 고유 좌표계</t>
+  </si>
+  <si>
+    <t>(2) UI : 스크린좌표계(픽셀)</t>
+  </si>
+  <si>
+    <t>4. 게임오브젝트와 UI단위계(좌표계) 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>public class Score : MonoBehaviour</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    GameObject G;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Text T;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Start is called before the first frame update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void Start()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        G = GameObject.Find("small_helmet_pig_sprites_by_chinzapep-d57z4bs_0");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print(gameObject);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        T = GetComponent&lt;Text&gt;(); //26번 라인의 RectTransform형 position 프로퍼티를 사용하기 위해서 찾는다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                  //왜냐하면 gameobject형에서는 RectTransform을 쓸수 없기 때문이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print(T);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        T.rectTransform.position = Camera.main.WorldToScreenPoint(G.transform.position);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    } /* scene좌표계의 돼지좌표값을 UI좌표계로 변환한 우항의 값을 Text UI좌표값으로 대입을 시키려면 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * 좌항의 UI의 좌표값(position)으로 UI의 좌표계 자료형인 RectTransform형 position 프로퍼티를 사용해야 한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * 만약 Transform형 position 프로퍼티를 좌항에서 사용하면 Text UI좌표값이 정상적으로 설정되지 못한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * 왜냐하면 Transform형 position 프로퍼티는 게임오브젝트의 위치값을 설정할때 사용하는 프로퍼티이고 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * UI의 위치값을 설정할때는 사용할 수 없기 때문이다 UI의 위치값을 설정할때는 반드시 RectTransform형</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * position 프로퍼티를 사용해야 한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       */</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Scene좌표계와 월드좌표계 변환방법 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// 클래스 Cat선언</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Cat.name.ppp() 에서 Cat은 클래스이고 name은 static선언한 필드고 ppp()는 Name 인스턴스안에 있는 메소드다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//ppp()는 메소드다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23.클래스 기반언어에서 메소드 호출의 한 예시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Cat을 갖다대보면 클래스임을 알수있고, 대문자라는 사실로도 클래스임을 알 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Name 자료형인 이유 : Name클래스에 있는 ppp()메소드를 호출 하기 위해서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// static 선언을 한이유 :  자주 사용하기때문에 매번 인스턴스를 만드는것이 비효율적이기 때문이다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>(3)코드 : PublicAPIAttribute GameObject Spike;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        float span = 1.0f;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        float delta = 0;</t>
-  </si>
-  <si>
-    <t>private void Update() {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        delta += Time.deltaTime;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if(DeltaSpeed &gt; span)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            DeltaSpeed = 0;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            GameObject go = Instantiate(spike);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">            int px = Random.Range(-6, 7);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            go.transform.position = new Vector3(px,7,0);</t>
-  </si>
-  <si>
-    <t>}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.collision.contact[] </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15. Prefabs(프리팹 복제)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)주의사항 : 2D프로젝트에서는 콜백안됨.</t>
-  </si>
-  <si>
-    <t>(2)2D프로젝트에선 2D형 컴퍼넌트,메소드를 사용할것 예외는 vector3</t>
-  </si>
-  <si>
-    <t>2.OnCollisionEnter()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)SortingLayer로 정렬하기 : Sprite Renderer 컴퍼넌트 -&gt; Sorting Layer -&gt; Add Sorting Layer -&gt; +버튼클릭 -&gt; Layer추가(숫자가 높을수록 앞에 있고 낮을수록 가려진다) -&gt;각 오브젝트 선택후Sorting Layer값선택</t>
-  </si>
-  <si>
-    <t>11.레이어로 정렬하기(오브젝트들이 화면에 겹쳐지는 순서)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)오브젝트 크기구하는 방법 : 콜라이더를 씌워본다. -&gt; 콜라이더의 사이즈값을 체크한다 ex) 사각형오브젝트에 박스콜라이더를 씌워서 사이즈 체크</t>
-  </si>
-  <si>
-    <t>2.배경이어붙이기(Crankie Box)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)메인 카메라 -&gt; background -&gt; 스포이드 눌러서 배경색 찍기</t>
-  </si>
-  <si>
-    <t>12.메인카메라 배경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)stackoverflow</t>
-  </si>
-  <si>
-    <t>(2)github</t>
-  </si>
-  <si>
-    <t>11.개발자가 알아야하는 사이트 목록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)Canvas 오브젝트 선택 -&gt; 인스펙터창에서 Canvas Scaler 컴퍼넌트의 UI Scale Mode를 scale with screen size 선택 -&gt; 내가 설치하려는 디바이스 해상도를 입력(비율로 적어도 OK) </t>
-  </si>
-  <si>
-    <t>(2)UI Scale Mode를 Constant Pixel Size로 선택하면 유니티에디터에서 보이는대로 안보일 확률이 크다 따라서 scale with sreen size를 선택해야 한다.(가장 선호도높은 디바이스를 찾은뒤 걔를 기준으로 UI를 구성한다)</t>
-  </si>
-  <si>
-    <t>1. 유니티 에디터에서 보이는대로 실제 디바이스에서 UI가 보이게 하는 방법(유니티에디터에서는 실제디바이스에서 보이는거랑 다를 수 있다.)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)모니터 픽셀 하나하나에 컬러값(RGBA A는 투명도)을 구하는 연산순서를 정의한것 따라서 이순서에 맞춰 연산을 해야된다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">예 )60Hz짜리 해상도 1920X1080 모니터의 경우 픽셀이 약 207만개, 60분의 1초마다 207만개의 픽셀의 컬러값을 계산해야 한다. 이계산과정은 GPU에서 수행한다. </t>
-  </si>
-  <si>
-    <t>예) 고성능 게임의 경우(조명환경이 복잡하거나 시시각각으로 환경이 변하는 경우) 각픽셀에 컬러값을 계산하는데 굉장히 많은 연산작업이 필요하게 된다. 따라서 모니터 주파수 60분의 1초마다 출력해야하는데</t>
-  </si>
-  <si>
-    <t>그걸 처리못해 버벅거리는 현상이 버퍼링 현상이다.</t>
-  </si>
-  <si>
-    <t>1. 렌더링 파이프라인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)기본적으로 scale with size모드를 사용해야 하며, 해상도 비율이 다른 디바이스에 대응하기 위해 UI 요소들으 배치가 가로방향 위주이면 Match값을 width &gt; height로 구성해주고, 세로방향 위주이면</t>
-  </si>
-  <si>
-    <t>Match값을 width &lt; height로 구성해준ㄴ다. 동일한 해상도 비율의 디바이스 간에는 Match값이 의미가 없음 Match값은 유니티 에디터에서 기준으로 삼은 해상도 비율과 다른 디바이스에 해당 앱이</t>
-  </si>
-  <si>
-    <t>설치되었을때 UI의 배치가 어떤식으로 조정할것인지에 대한 factor(어떤요인이 되는 변수)값임 따라서, 유니티 에디터에서 기준으로 삼은 해상도 비율과 일치하는 디바이스에서는 Match값은 의미가 없다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.Canvas 옵션설정 방법 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)메모리상에 오직 인스턴스가 하나만 존재해야 하는 클래스 (예를들면 장치의 부품들처럼 하나만 존재하는 부품을 소스코드에서 가져다 사용해야 될 경우 그부품 클래스의 인스턴스가 여러개 존재하는것은 모순이다.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2)만드는 방법 : 생성자를 private으로 만든다( private Store() { } ) -&gt; static 필드로 객체 생성(  private static   Store instance = new Store(); ) </t>
-  </si>
-  <si>
-    <t>-&gt; 객체의 getter 구현( public static Store getInstance() {return instance}</t>
-  </si>
-  <si>
-    <t>(3)유니티에서 싱글톤 만드는법 :</t>
-  </si>
-  <si>
-    <t>16.싱글톤(single tone)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)추상클래스는 추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)를 가지고있는 클래스</t>
-  </si>
-  <si>
-    <t>(2)추상클래스를 상속한 자식클래스에서 그 추상메소드를 오버라이딩해서 추상메소드를 사용할 수 있는 메소드로 만든다.(구현) extends사용</t>
-  </si>
-  <si>
-    <t>(3)단,  자식클래스에서 추상클래스의 추상메소드를 오버라이딩 할 의무는 없다(선택이다  extends 사용)</t>
-  </si>
-  <si>
-    <t>(1)상수,추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)만 가지고있는 클래스 필드,일반메소드는 존재할 수 없음.</t>
-  </si>
-  <si>
-    <t>(2)자식인터페이스에서 상속 가능(extends) 자식인터페이스끼리 상속</t>
-  </si>
-  <si>
-    <t>(3)자식클래스에서 상속하는경우 반드시 추상클래스의 추상메소드를 의무적으로 구현해줘야함(implements 사용)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4)추상클래스와의 차이점 : 추상메소드의 구현을 자식클래스에서 강제적으로 하면 인터페이스, 선택이면 추상클래스 이다. 그리고 추상클래스와 인터페이스는 공통적으로 다형성(오버라이딩,오버로딩) 구현의 수단이다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">다만 인터페이스가 추상클래스보다 더 강제성을 띈다. </t>
-  </si>
-  <si>
-    <t>(1)사용법 : 참조변수.GetHashCode()</t>
-  </si>
-  <si>
-    <t>17.추상 클래스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18.인터페이스(interface)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19.인스턴트의 주소값을 알려주는 메소드(GetHashCode())</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 게임시작시 필요한 오브젝트를 미리 만들어서 특정영역(게임화면 밖)에 배치해두고 필요할때마다 갖다쓰고 다쓰면 원래위치로 반환 게임실행중에 해당오브젝트가 새로 생성되거나 삭제되지 않는다.</t>
-  </si>
-  <si>
-    <t>(2)프리팹공장 방식과의 차이점 : 오브젝트를 미리만들지않고 게임실행중에 필요할때마다 Instantiate()를 사용해서 복제하고 필요없으면 Destroy()메소드로 삭제한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)장단점 : 장점은 게임실행중에 삭제(가비지 컬렉션)작업이 없기 때문에 쾌적하다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">단점 : 게임시작시에 오브젝트를 만드는데 로딩시간이 필요하다.(프리팹공장방식에선 Destroy()메소드를 호출하여 삭제하는것이 실질적으로는 가비지컬렉션 작업이 발생하는것 이며 가비지컬렉션은 </t>
-  </si>
-  <si>
-    <t>메인쓰레드(어떤 주작업영역(UI나 핵심적인 작업등)상에서 작업처리가 되기 때문에 게임이 중지된다. 사용자가 느끼기에 버퍼링이 생기는것 처럼 느끼게 된다.)</t>
-  </si>
-  <si>
-    <t>3.오브젝트 풀링(object pooling)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)특징 : 배열인데도 배열명이 상수가 아니라 참조변수이다.</t>
-  </si>
-  <si>
-    <t>(2)만드는법 : GameObject[] platforms = new GameObject[count]; // new연산자를 사용한다. 즉 우항의 배열공간이 heap영역에 생긴다. 그리고 그것뿐만이 아니라 결론적으로 클래스 인스턴스 처럼 생긴다. 그안에 배열데이터가 들어간다</t>
-  </si>
-  <si>
-    <t>20. c#에서의 배열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LLVM ERROR: IO failure on output stream: No space left on device</t>
-  </si>
-  <si>
-    <t>PLEASE submit a bug report to https://github.com/android-ndk/ndk/issues and include the crash backtrace.</t>
-  </si>
-  <si>
-    <t>Stack dump:</t>
-  </si>
-  <si>
-    <t>Program arguments: "C:/Program Files/Unity/Hub/Editor/2022.3.17f1/Editor/Data/PlaybackEngines/AndroidPlayer/NDK/toolchains/llvm/prebuilt/windows-x86_64/bin/llvm-objcopy.exe" --only-keep-debug Library/Bee/artifacts/Android/libunity/armeabi-v7a/unstripped/libunity.so Library/Bee/artifacts/Android/libunity/armeabi-v7a/libunity.dbg.so</t>
-  </si>
-  <si>
-    <t>UnityEngine.GUIUtility:ProcessEvent (int,intptr,bool&amp;)</t>
-  </si>
-  <si>
-    <t>(1)원인 : 하드용량 부족</t>
-  </si>
-  <si>
-    <t>(2)대처법 : 이런 에러싸인이 나오면 pc의 하드용량이 모자란지 확인해본다. 하드용량을 충분히 잡아준뒤 다시 빌드한다.</t>
-  </si>
-  <si>
-    <t>(1)원인 : 같은 프로젝트안에 동명의 Camera 스크립트가 존재 하기때문(Camera.mainScreenToWorldPoint(Input.mousePosition); 이 메소드를 호출할때 유니티에서 제공하는 Camera클래스와 이름이 같기때문에 에러가 발생)</t>
-  </si>
-  <si>
-    <t>(2)대처법 : 유니티 라이브러리에서 제공하는 클래스이름과 같은 이름으로 스크립트를 만들지 않는다.(좋은이름 짓는 방법 : 지으려는 이름에 _자기이름을 같이 사용한다거나 해서 겹치지않게 한다.)</t>
-  </si>
-  <si>
-    <t>6.Building Library\Bee\artifacts\Android\libunity\armeabi-v7a\libunity.dbg.so failed with output:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6-1 Assets\Script\slingShotScript.cs(32,50): error CS0117: 'Camera' does not contain a definition for 'main'</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 매개변수로 설정한 디바이스상(스크린좌표계,픽셀단위를 사용)의 좌표를 유니티의 월드좌표계(유니티 자체 단위계(눈금))로 변환해준다 단, Z값은 카메라의 Z값으로 반환 즉 카메라랑 선상에 있어서 안보인다</t>
-  </si>
-  <si>
-    <t>(2)대처법 : 2D일때는 vector2로 명시적형변환을 해준다.</t>
-  </si>
-  <si>
-    <t>(2-1) 예시 스크립트 : transform.position = (Vector2)Camera.main.ScreenToWorldPoint(Input.mousePosition);</t>
-  </si>
-  <si>
-    <t>7. Camera.main.ScreenToWorldPoint();</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 :  오브젝트의 궤적(발자취)을 그려주는 컴퍼넌트</t>
-  </si>
-  <si>
-    <t>(2)사용법</t>
-  </si>
-  <si>
-    <t>(2-1) Materials : 설정안하면 기본값으로 보라색 색종이(사각형)으로 나옴 머터리얼을 다른값으로 설정하면 머터리얼대로 나옴 단, 레이어 정렬이 적용되는것과 안되는것이 있음 적용되는것은 파티클만 가능</t>
-  </si>
-  <si>
-    <t>1.Trail Renderer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)setActive는 GameObject클래스 소속의 메소드고 GameObject클래스 + 상속한 자식클래스의 참조변수에서만 사용할 수 있다. 따라서 GameObject와 상속관계가 없는 Component형 참조변수(예 : TraillRenderer)를 통해서는 호출 할 수 없다</t>
-  </si>
-  <si>
-    <t>(2)따라서 Component형 참조변수를 활성화시키거나 비활성화 시킬때는 SetActive를 사용할 수 없고, Component클래스에서 제공하는 enabled 프로퍼티를 사용해서 활성화,비활성화 처리를 할 수있다.</t>
-  </si>
-  <si>
-    <t>16. setActive와 Enabled의 차이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)동기식(sync) : 동기식은 메소드가 호출되면 메소드가 실행종료될때까지 다음라인으로 안넘어가고 대기상태</t>
-  </si>
-  <si>
-    <t>(2)비동기식(async) : 비동기식은 메소드호출되고 메소드의 종료 여분상관없이 다음라인으로 넘어감 (예시: StartCoroutine)</t>
-  </si>
-  <si>
-    <t>21.메소드의 동작방식(동기식,비동기식)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)GameObject클래스와 아무런 상속관계가 없다. 따라서 서로간에 형변환이 불가능하다. </t>
-  </si>
-  <si>
-    <t>(2)하지만 Unity에서는 Scene에 추가된 모든자로형은 GameObject형으로도 취급되므로 형변환이 가능하다. UNITY에서만 해당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.UI 자료형(예 : Slider) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)힘의 공식 : F = ma // f는 힘,m은 질량, a는 가속도 </t>
-  </si>
-  <si>
-    <t>(1)E = mc^2 // E는 에너지,m는 질량,c는 광속도</t>
-  </si>
-  <si>
-    <t>(1) 하는법 :</t>
-  </si>
-  <si>
-    <t>3.뉴턴의 운동방정식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.Rigidbody 컴퍼넌트 질량값 조절</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.아인슈타인의 에너지 공식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) if(!(collision.gameObject.tag.Equals("Ground"))) //코드의 맨앞부분에 적는다 햇갈린다면 ()를 사용해서 명시적으로 구분을 해줄것</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            x.SetTrigger("New Trigger");</t>
-  </si>
-  <si>
-    <t>22. !(not) 붙이는위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)일단 필요한 자료형 이름을 소스코드에 적는다(using이 안되있다면 빨간줄이 그어진다)</t>
-  </si>
-  <si>
-    <t>(2)빨간줄 그어지고 빨간색 X아이콘이 나타나고 그걸 클릭한다</t>
-  </si>
-  <si>
-    <t>(3)목록으로 오류사항을 해결할수 있는 해결책을 제시해준다 그중에서 선택한다.</t>
-  </si>
-  <si>
-    <t>1.자료형의 namespace가 기억안날때</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)https://jinhyo98.tistory.com/436 참고</t>
-  </si>
-  <si>
-    <t>12.폴더내 특정 키워드를 가진 파일찾기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)게임오브젝트 : 유니티 내에서 사용하는 고유 좌표계</t>
-  </si>
-  <si>
-    <t>(2) UI : 스크린좌표계(픽셀)</t>
-  </si>
-  <si>
-    <t>4. 게임오브젝트와 UI단위계(좌표계) 차이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>public class Score : MonoBehaviour</t>
-  </si>
-  <si>
-    <t>{</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    GameObject G;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Text T;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    // Start is called before the first frame update</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    void Start()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        G = GameObject.Find("small_helmet_pig_sprites_by_chinzapep-d57z4bs_0");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        print(gameObject);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        T = GetComponent&lt;Text&gt;(); //26번 라인의 RectTransform형 position 프로퍼티를 사용하기 위해서 찾는다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  //왜냐하면 gameobject형에서는 RectTransform을 쓸수 없기 때문이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        print(T);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        T.rectTransform.position = Camera.main.WorldToScreenPoint(G.transform.position);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    } /* scene좌표계의 돼지좌표값을 UI좌표계로 변환한 우항의 값을 Text UI좌표값으로 대입을 시키려면 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * 좌항의 UI의 좌표값(position)으로 UI의 좌표계 자료형인 RectTransform형 position 프로퍼티를 사용해야 한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * 만약 Transform형 position 프로퍼티를 좌항에서 사용하면 Text UI좌표값이 정상적으로 설정되지 못한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * 왜냐하면 Transform형 position 프로퍼티는 게임오브젝트의 위치값을 설정할때 사용하는 프로퍼티이고 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * UI의 위치값을 설정할때는 사용할 수 없기 때문이다 UI의 위치값을 설정할때는 반드시 RectTransform형</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * position 프로퍼티를 사용해야 한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       */</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Scene좌표계와 월드좌표계 변환방법 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>// 클래스 Cat선언</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>// Cat.name.ppp() 에서 Cat은 클래스이고 name은 static선언한 필드고 ppp()는 Name 인스턴스안에 있는 메소드다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>//ppp()는 메소드다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>23.클래스 기반언어에서 메소드 호출의 한 예시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>// Cat을 갖다대보면 클래스임을 알수있고, 대문자라는 사실로도 클래스임을 알 수 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>// Name 자료형인 이유 : Name클래스에 있는 ppp()메소드를 호출 하기 위해서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>// static 선언을 한이유 :  자주 사용하기때문에 매번 인스턴스를 만드는것이 비효율적이기 때문이다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.spirte sheet 쪼개기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13. asset과 Scene창의 게임오브젝트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)Scene창에 넣는 순간부터 그 에셋들은 GameObject가 되고 그자료형은 모두 GameObject형이 된다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)프리팹도 자료형은 GameObject형이다(Scene창에 있던 게임오브젝트를 다시 asset에 넣은것이므로)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)하이러라키창에 있는 게임오브젝트는 Scene에 출연 확정된 에셋이고, asset창에 있는 프리팹들은 아직 scene에 포함이 되지 않은 게임오브젝트다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉, 차이점은 다 같은 GameObject형이지만 Scene의 존재여부가 차이점이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2281,22 +2303,22 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -2304,42 +2326,42 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -2355,27 +2377,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -2854,152 +2876,152 @@
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.4">
@@ -3009,7 +3031,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.4">
@@ -3019,37 +3041,37 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.4">
       <c r="J156" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.4">
       <c r="J157" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="161" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J161" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="163" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J163" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="164" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J164" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="168" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J168" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -3066,22 +3088,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -3322,47 +3344,47 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
@@ -3402,52 +3424,52 @@
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>402</v>
+        <v>535</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
@@ -3457,22 +3479,22 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>410</v>
+        <v>536</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
@@ -3482,22 +3504,22 @@
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -3569,7 +3591,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5B0EB0-3A18-406B-BDAC-7BBC8487A206}">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -3699,42 +3721,67 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>422</v>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -3965,27 +4012,27 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -4001,67 +4048,67 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -4092,42 +4139,42 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -4168,22 +4215,22 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -4485,7 +4532,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>357</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
@@ -4520,102 +4567,102 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4952,57 +4999,57 @@
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
@@ -5012,27 +5059,27 @@
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
@@ -5057,47 +5104,47 @@
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -5113,22 +5160,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -5154,17 +5201,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -5245,32 +5292,32 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F227DD-DA44-4D7F-BF9B-AAF3FC3868FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB0F16F-1D0F-45BE-8CB1-94257E4B65E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="5" activeTab="15" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="6" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="842">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -605,9 +605,6 @@
     <t>(1)center : 센터는 오브젝트의 중심점이 지형학적 중심</t>
   </si>
   <si>
-    <t>(2)pivot : 피봇은 발바닥이 기준점</t>
-  </si>
-  <si>
     <t>4.center 와 pivot</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2805,6 +2802,118 @@
   </si>
   <si>
     <t>(1)적용하려는 오브젝트의 레이어를 각각 만들고 레이어를 씌운다 &gt; edit &gt; project settings &gt; phyhics2D &gt; layer collison matrix 로 간뒤 충돌이 일어나면 안되는 오브젝트의 체크표시 해제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)pivot : 피봇은 transform의 기준점, 변경하는 법은 asset에서(하이러라키 X) 바꾸려는 이미지 선택 &gt; sprite editor(굳이 안들어가고 밖에서 해도 됨) &gt; pivot을 수정 &gt; apply, shift로 다중선택 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18. 게임오브젝트 정렬 &amp; 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)정렬하려는 오브젝트 선택후 V를 누른채로 위치하려는 상대물에 드래그 시켜서 배치한다(상대물의 센터나 꼭짓점부분을 선택할 수 있다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8.GetAxisRaw() </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)axis값을 비연속적인값으로 변환(-1,0,1 세가지의 값만 가진다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)예시 : axisH = Input.GetAxisRaw("Horizontal");</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9.Linecast() </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 매개변수 3개를 가지며 첫번째 매개변수와 두번째 매개변수 사이의 거리안에(범위) 세번째 매개변수(레이어)가 존재 하면 true 없으면 false 리턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>붉은선 : 첫번째 매개변수, 파란선 : 두번째 매개변수 검은점 : pivot, 주황색선은 첫번째 매개변수와 두번째 매개변수 사이의 거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transform의 기준점은 pivot이기 때문에 pivot을 옮겨서 정교하게 구현하기 위해서다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) 예시 : onGround = Physics2D.Linecast(transform.position,transform.position - (transform.up * 0.1f),groundLayer);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16. ForceMode2D.Impulse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 물리에서 이론상 0초동안 무한의 힘을 준다(유니티에서는 힘을 분산시키는게 아니라 힘을 모아서 방출한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector2 jumpPw = new Vector2(0, jump);</t>
+  </si>
+  <si>
+    <t>rbody.AddForce(jumpPw, ForceMode2D.Impulse);</t>
+  </si>
+  <si>
+    <t>//ForceMode2D.Impulse는 작은힘으로도 크게 가능하다(물리적으로 보면 이론상 0의 시간동안 무한대의 힘을 주는게 Impulse다)</t>
+  </si>
+  <si>
+    <t>//자동차의 엔진이나 모터등을 정지해있던 상태에서 처음 구동시킬때랑 비슷한 예이다(캐피시터)</t>
+  </si>
+  <si>
+    <t>3. physics material 2D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) Friction : 마찰계수(0이면 없고 1이면 최대)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)만드는법 : 프로젝트 &gt; 2D &gt; physics material 2D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)bounciness : 물체 반동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5)static 필드의 의미 : scene이 전환되어도 다른 scene에서 사라지지않고 사용가능하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10. Canvas랑 Scene 겹쳐서 보는 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) canvas 선택 &gt; render mode를 scene space camera로 선택 &gt; render camera를 main camera로 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11. Image 크기 조절 하는 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Preserve Aspect 가로 세로 비 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Set Native size 원본 이미지 크기로 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10. 버튼클래스의 interactable 프로퍼티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)버튼의 이미지가 반투명해지고 상호작용이 막힌다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3250,6 +3359,364 @@
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="직사각형 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02DA2E21-D818-EBD6-E544-445CC871392B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="23660100"/>
+          <a:ext cx="3322320" cy="205740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="직선 화살표 연결선 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D3AA7F9-98F3-0EDE-D87C-389F81D07A30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15240" y="23644860"/>
+          <a:ext cx="4373880" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="직선 화살표 연결선 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4366BC-962F-DA99-A73F-FB15CD0C6DC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="23762970"/>
+          <a:ext cx="4381500" cy="102870"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>534360</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>51900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38760</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>34320</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="15" name="잉크 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1204920" y="23475780"/>
+            <a:ext cx="174960" cy="203400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="15" name="잉크 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1198787" y="23469660"/>
+              <a:ext cx="187225" cy="215640"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>593400</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>9840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>625080</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>46560</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="18" name="잉크 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1263960" y="23654700"/>
+            <a:ext cx="31680" cy="36720"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="18" name="잉크 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1257770" y="23648580"/>
+              <a:ext cx="44061" cy="48960"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="직선 연결선 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32C3C467-3D66-B670-623E-F5BA44F74E4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1280160" y="23690580"/>
+          <a:ext cx="0" cy="182880"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="76200">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3341,7 +3808,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3610,7 +4077,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3659,7 +4126,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4426,7 +4893,110 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>15804</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>177560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF041C3D-0922-76AD-7A6A-67512EC750F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14142720"/>
+          <a:ext cx="4039164" cy="2829320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-30T11:31:23.141"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">39 3 24575,'45'-1'0,"-23"0"0,1 1 0,33 4 0,-53-4 0,0 1 0,1 0 0,-1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,-1 1 0,0-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 6 0,-1-7 0,-1 1 0,1 0 0,-1-1 0,1 1 0,-1 0 0,0-1 0,0 1 0,0 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 1 0,1-1 0,-1 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,-1-1 0,1 1 0,-4 1 0,-1-1 0,0 1 0,0-1 0,0 0 0,0 0 0,0-1 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1-1 0,-14-2 0,17 3 0,1-1 0,-1 0 0,0 0 0,1-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,0 0 0,-1 0 0,2 0 0,-1-1 0,0 1 0,0-1 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,1-1 0,-1 1 0,0 0 0,1-1 0,-2-4 0,-3-34-1365,5 23-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2370.02">187 236 24575,'0'21'0,"1"-9"0,-1 0 0,-1 1 0,-3 19 0,3-27 0,-1-1 0,1 0 0,-1 1 0,0-1 0,0 0 0,0 0 0,0 0 0,-1-1 0,1 1 0,-1 0 0,0-1 0,0 0 0,-7 5 0,-16 13 0,-41 36 0,61-51 0,1-1 0,-1 1 0,1 1 0,1-1 0,-1 1 0,1 0 0,1 0 0,-6 11 0,9-17-31,-1 0 0,1-1 0,0 1 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,1 1 0,-1 0-1,0 0 1,1 0 0,-1-1 0,1 1 0,-1 0 0,1-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,1 0 0,11 1-6795</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3528.54">187 363 24575,'7'0'0,"7"4"0,3 4 0,4 2 0,0 1 0,2 1 0,0-3 0,-5 0 0,0 0 0,-5 1 0,1 3 0,0-1 0,-2 1 0,1 2 0,1 2 0,3-2 0,-2-3-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4653.05">187 257 24575,'-7'0'0,"-3"-3"0,-2-2 0,-4 0 0,-2 2 0,2-3 0,-4-1 0,-2 2 0,0 1 0,2 5 0,6 6 0,5 1-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5648.22">251 194 24575,'7'0'0,"6"4"0,5 4 0,2 5 0,6 0 0,1-2 0,4 0 0,-4 3 0,-2 2 0,-3-2 0,-4-3-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-30T11:31:32.855"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">87 14 24575</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2997.74">87 14 24575,'-2'1'0,"0"-1"0,0 0 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 1 0,1-1 0,-1 0 0,1 1 0,0-1 0,-1 1 0,1 0 0,-2 2 0,3 0 0,0-1 0,0 1 0,-1-1 0,1 1 0,-1-1 0,0 0 0,0 1 0,-1-1 0,1 0 0,0 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,-1-1 0,-3 4 0,6-6 0,-1 0 0,1 0 0,-1 1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1-1 0,1 1 0,-1 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,0-1 0,0 1 0,-1-1 0,1 1 0,0 0 0,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 1 0,1-1 0,0 1 0,0-1 0,-4-26 0,4 26 0,0-2 0,0 0 0,0-1 0,0 1 0,0-1 0,1 1 0,0 0 0,-1 0 0,1-1 0,0 1 0,1 0 0,-1 0 0,0 0 0,3-4 0,-3 6 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,1-1 0,-1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,1 0 0,-1 0 0,0-1 0,1 1 0,-1 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 1 0,0 0 0,0-1 0,1 1 0,-1 0 0,2 1 0,-1-1 0,0 1 0,0-1 0,0 1 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 1 0,1-1 0,-1 1 0,0 0 0,1-1 0,-1 1 0,0-1 0,-1 1 0,1 0 0,0-1 0,-1 1 0,-1 4 0,2-7 1,0 0 1,0 0-1,-1 0 0,1 1 0,0-1 1,0 0-1,0 0 0,0 0 0,0 0 0,0 0 1,0 0-1,-1 0 0,1 0 0,0 0 0,0 1 1,0-1-1,0 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 0 0,0 0 0,0 0 1,-1 0-1,1 0 0,0 0 0,0 0 0,0 0 1,0 0-1,-1 0 0,1 0 0,0-1 1,0 1-1,0 0 0,0 0 0,0 0 0,0 0 1,-1 0-1,1 0 0,0 0 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 0,0 0 1,-1 0-1,1 0 0,0 0 0,0-1 0,0 1 1,0 0-1,0 0 0,0 0 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 0,0 0 1,0 0-1,0 0 0,0-1 0,0 1 0,0 0 1,-1-12-1449,3 2-5379</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4801,37 +5371,37 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -4839,80 +5409,80 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
+        <v>792</v>
+      </c>
+      <c r="B40" t="s">
         <v>793</v>
-      </c>
-      <c r="B40" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -4978,47 +5548,47 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -5034,27 +5604,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -5065,7 +5635,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF95FB6-E86C-4F62-8755-AC901C3CF614}">
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -5295,157 +5865,157 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
@@ -5453,27 +6023,27 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B94" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
@@ -5483,207 +6053,197 @@
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
-        <v>381</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A116" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A120" t="s">
-        <v>435</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>437</v>
+        <v>433</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A126" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>441</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A131" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>446</v>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A141" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A142" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A145" t="s">
-        <v>714</v>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>493</v>
+        <v>714</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A149" t="s">
-        <v>10</v>
+        <v>713</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
@@ -5693,67 +6253,67 @@
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>13</v>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>545</v>
+        <v>491</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
-        <v>547</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A159" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>10</v>
+        <v>547</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>552</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>248</v>
+        <v>549</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.4">
@@ -5763,126 +6323,141 @@
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>554</v>
+        <v>247</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>248</v>
+        <v>552</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>13</v>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A170" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>559</v>
+        <v>247</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A174" t="s">
         <v>558</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A173" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A177" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B178" t="s">
+      <c r="A178" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A179" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>582</v>
+        <v>562</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B181" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A183" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B184" t="s">
+        <v>583</v>
+      </c>
+      <c r="E184" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B185" t="s">
+        <v>582</v>
+      </c>
+      <c r="E185" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B186" t="s">
         <v>584</v>
       </c>
-      <c r="E181" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B182" t="s">
-        <v>583</v>
-      </c>
-      <c r="E182" t="s">
+      <c r="E186" t="s">
         <v>587</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B183" t="s">
-        <v>585</v>
-      </c>
-      <c r="E183" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A185" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A186" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A187" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>670</v>
+        <v>666</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A192" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>722</v>
+        <v>668</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>723</v>
+        <v>669</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A196" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A197" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -5898,22 +6473,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -5974,122 +6549,122 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
@@ -6099,12 +6674,12 @@
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
@@ -6114,35 +6689,35 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
+        <v>801</v>
+      </c>
+      <c r="G55" t="s">
         <v>802</v>
-      </c>
-      <c r="G55" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
@@ -6152,7 +6727,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
@@ -6162,117 +6737,117 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
@@ -6282,12 +6857,12 @@
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
@@ -6297,57 +6872,57 @@
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
@@ -6357,22 +6932,22 @@
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.4">
@@ -6382,197 +6957,197 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B119" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B121" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.4">
@@ -6582,17 +7157,17 @@
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.4">
@@ -6602,7 +7177,7 @@
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.4">
@@ -6612,7 +7187,7 @@
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.4">
@@ -6622,7 +7197,7 @@
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
@@ -6632,52 +7207,52 @@
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.4">
@@ -6687,17 +7262,17 @@
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.4">
@@ -6707,7 +7282,7 @@
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.4">
@@ -6717,7 +7292,7 @@
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.4">
@@ -6727,7 +7302,7 @@
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.4">
@@ -6737,52 +7312,52 @@
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.4">
@@ -6792,17 +7367,17 @@
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
@@ -6812,7 +7387,7 @@
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
@@ -6822,7 +7397,7 @@
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.4">
@@ -6832,7 +7407,7 @@
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.4">
@@ -6842,112 +7417,112 @@
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -7020,7 +7595,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5B0EB0-3A18-406B-BDAC-7BBC8487A206}">
-  <dimension ref="A1:A94"/>
+  <dimension ref="A1:A106"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -7065,7 +7640,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
@@ -7075,177 +7650,187 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>813</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>813</v>
+        <v>812</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>815</v>
       </c>
     </row>
   </sheetData>
@@ -7257,7 +7842,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A320F51B-952E-44A4-8797-50ACF70F49CD}">
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -7337,22 +7922,22 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -7462,87 +8047,122 @@
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K74" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K80" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>811</v>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>829</v>
       </c>
     </row>
   </sheetData>
@@ -7559,127 +8179,127 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -7690,172 +8310,197 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A67CEF4-BE01-4763-BDC6-975F09EE47AA}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H25" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H26" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>648</v>
+        <v>647</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G75" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="76" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G76" t="s">
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -7897,47 +8542,47 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -7968,42 +8613,42 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -8019,17 +8664,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -8045,77 +8690,77 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
@@ -8125,12 +8770,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
@@ -8140,192 +8785,192 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -8341,270 +8986,270 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>
@@ -8624,52 +9269,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
   </sheetData>
@@ -8686,97 +9331,97 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
@@ -8786,12 +9431,12 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
@@ -8801,7 +9446,7 @@
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
@@ -8811,7 +9456,7 @@
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
@@ -8836,7 +9481,7 @@
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -8846,7 +9491,7 @@
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
@@ -8856,7 +9501,7 @@
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
@@ -8866,7 +9511,7 @@
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
@@ -8876,7 +9521,7 @@
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.4">
@@ -8886,42 +9531,42 @@
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
@@ -8936,57 +9581,57 @@
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F56" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F58" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F59" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F63" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F65" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F66" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F68" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="72" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F72" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F73" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F74" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
@@ -9021,7 +9666,7 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
@@ -9086,22 +9731,22 @@
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -9113,7 +9758,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22FACE01-8634-40CF-BA9C-3264EEAD61A5}">
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -9273,27 +9918,27 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
@@ -9303,7 +9948,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
@@ -9313,7 +9958,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
@@ -9323,7 +9968,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
@@ -9333,7 +9978,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
@@ -9343,117 +9988,117 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
@@ -9463,27 +10108,27 @@
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
@@ -9508,52 +10153,103 @@
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>407</v>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H107" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H108" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>841</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9564,22 +10260,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -9590,32 +10286,52 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD10C7B-DC9E-441F-88CC-55E83D279026}">
-  <dimension ref="A10:A15"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>831</v>
+      </c>
+    </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>411</v>
+        <v>832</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB0F16F-1D0F-45BE-8CB1-94257E4B65E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90954AC-C0EA-4E51-BFE5-AB09F86BC2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="6" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="915">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -426,16 +426,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1) 프레임 간격 사이에 경과 시간</t>
-  </si>
-  <si>
-    <t>(2)de += Time.deltaTime; //프레임간에 경과시간을 누적하여 더함.</t>
-  </si>
-  <si>
-    <t>1.time.deltaTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2.하이러라키 창에 존재하는 게임오브젝트와 프로젝트창에 리소스는 다르다.</t>
   </si>
   <si>
@@ -2914,6 +2904,248 @@
   </si>
   <si>
     <t>(1)버튼의 이미지가 반투명해지고 상호작용이 막힌다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>using System.Collections;</t>
+  </si>
+  <si>
+    <t>using System.Collections.Generic;</t>
+  </si>
+  <si>
+    <t>public class CameraManager : MonoBehaviour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public float leftLimit = 0.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public float rightLimit = 0.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public float topLimit = 0.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public float bottomLimit = 0.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        GameObject player = GameObject.FindGameObjectWithTag("Player");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (player != null)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Debug.Log("a");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            float x = player.transform.position.x;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            float y = player.transform.position.y;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            float z = transform.position.z;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if (x &lt; leftLimit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                x = leftLimit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            else if (x &gt; rightLimit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                x = rightLimit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if (y &lt; bottomLimit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                y = bottomLimit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            else if (y &gt; topLimit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                y = topLimit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Vector3 v3 = new Vector3(x, y, z);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            transform.position = v3;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public GameObject subScreen;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if (subScreen != null)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                y = subScreen.transform.position.y;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                z = subScreen.transform.position.z;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                subScreen.transform.position = v;</t>
+  </si>
+  <si>
+    <t>(1)원리 : 카메라(먼배경)와 배경(가까운 배경)과 바닥의 속도를 달리 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)기대효과 : 실제로 기차안에서 밖을 보는것같은 원근감을 갖게 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                Vector3 v = new Vector3(x / 2.0f, y, z); //camera의 x좌표의 절반을 subScreen에 적용 2.0값이 속도차를 나게 하는 코드이므로 상황에 맞게 2.0값을 바꿔서 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 스크립트로 구현한 추적 카메라 (limit 설정,sub screen을 이용한 입체감)(side view project 참고)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.time.deltaTime과 fixedDeltaTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)time.deltaTime : 프레임 간격 사이에 경과 시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1-2)de += Time.deltaTime; //프레임간에 경과시간을 누적하여 더함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)fixedDeltaTime : FixedUpdate 메서드가 호출되는 간격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 카메라 스크롤 하는법(카메라 강제 이동)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>public bool isForceScrollX = false;</t>
+  </si>
+  <si>
+    <t>public float forceSpeedX = 0.5f;</t>
+  </si>
+  <si>
+    <t>public bool isForceScrollY = false;</t>
+  </si>
+  <si>
+    <t>public float forceSpeedY = 0.5f;</t>
+  </si>
+  <si>
+    <t>void Update()</t>
+  </si>
+  <si>
+    <t>(1)이 스크립트를 카메라한테 넣은 후 스크롤 시킬 축을 체크한다(isForceScrollX 또는 isForceScrollY)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    GameObject player = GameObject.FindGameObjectWithTag("Player");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (player != null)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Debug.Log("a");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        float x = player.transform.position.x;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        float y = player.transform.position.y;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        float z = transform.position.z;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (isForceScrollX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            x = transform.position.x + (forceSpeedX * Time.deltaTime);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (x &lt; leftLimit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            x = leftLimit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        else if (x &gt; rightLimit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            x = rightLimit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (isForceScrollY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            y = transform.position.y + (forceSpeedY * Time.deltaTime);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (y &lt; bottomLimit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            y = bottomLimit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        else if (y &gt; topLimit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            y = topLimit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vector3 v3 = new Vector3(x, y, z);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        transform.position = v3;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (subScreen != null)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            y = subScreen.transform.position.y;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            z = subScreen.transform.position.z;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Vector3 v = new Vector3(x / 2.0f, y, z); //camera의 x좌표의 절반을 subScreen에 적용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            subScreen.transform.position = v;</t>
+  </si>
+  <si>
+    <t>public float leftLimit = 0.0f;</t>
+  </si>
+  <si>
+    <t>public float rightLimit = 0.0f;</t>
+  </si>
+  <si>
+    <t>public float topLimit = 0.0f;</t>
+  </si>
+  <si>
+    <t>public float bottomLimit = 0.0f;</t>
+  </si>
+  <si>
+    <t>4. 화면에서 벗어날 때 게임오버 시키는 법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)카메라의 자식으로 empty를 만들어서 배치한뒤 스크립트에서 tag 또는 layer(잘 사용X)로 충돌처리를 한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) 다른방법 : (1)의 과정에서 empty를 프리팹화 시킨뒤 프리팹화 된 empty를 배치해서 사용한다(sideview 게임 참고)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. 스크립트 이름이랑 클래스 이름이 다르면 재접속</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2995,6 +3227,55 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>23673</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>68579</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>214406</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75B9FB04-0C01-E1DC-17BC-F96FB94BAEC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="10188753"/>
+          <a:ext cx="6103619" cy="3063473"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3039,7 +3320,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3264,7 +3545,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3357,7 +3638,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3715,19 +3996,19 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>3054</xdr:colOff>
-      <xdr:row>147</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3765,13 +4046,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>160</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>205740</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>282541</xdr:colOff>
-      <xdr:row>172</xdr:row>
+      <xdr:row>175</xdr:row>
       <xdr:rowOff>2247</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3808,7 +4089,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4077,7 +4358,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4126,7 +4407,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -5296,7 +5577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B5B9BE-0D1B-456B-B9E1-2DF1026954E4}">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -5316,22 +5597,22 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
@@ -5341,7 +5622,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
@@ -5351,57 +5632,57 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -5409,85 +5690,91 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B40" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>773</v>
+        <v>770</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>914</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5548,47 +5835,47 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -5604,27 +5891,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -5745,277 +6032,277 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
@@ -6023,27 +6310,27 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B94" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
@@ -6053,207 +6340,207 @@
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.4">
@@ -6263,7 +6550,7 @@
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
@@ -6273,32 +6560,32 @@
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.4">
@@ -6308,42 +6595,42 @@
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.4">
@@ -6353,111 +6640,111 @@
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B181" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B184" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E184" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B185" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E185" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B186" t="s">
+        <v>581</v>
+      </c>
+      <c r="E186" t="s">
         <v>584</v>
-      </c>
-      <c r="E186" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -6473,22 +6760,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -6499,1030 +6786,1035 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194DBF29-D361-403B-8094-6B4DBAD9B202}">
-  <dimension ref="A1:G267"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>871</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>872</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>126</v>
+        <v>873</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>211</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>225</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>524</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>526</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>233</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>253</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>254</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>796</v>
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>503</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>798</v>
+        <v>793</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>801</v>
-      </c>
-      <c r="G55" t="s">
-        <v>802</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
-        <v>3</v>
+        <v>795</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>800</v>
+        <v>798</v>
+      </c>
+      <c r="G58" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>796</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>406</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
-        <v>256</v>
+        <v>403</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>274</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>308</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>379</v>
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A79" t="s">
-        <v>378</v>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>407</v>
+        <v>380</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A86" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>288</v>
+        <v>387</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>289</v>
+        <v>388</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>389</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>292</v>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>408</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>394</v>
+        <v>289</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>398</v>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>396</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>404</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>400</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>406</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>596</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A117" t="s">
-        <v>479</v>
+        <v>403</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B119" t="s">
-        <v>593</v>
+      <c r="A119" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>597</v>
+        <v>476</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B121" t="s">
-        <v>594</v>
+      <c r="A121" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B122" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A124" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A125" t="s">
-        <v>533</v>
+      <c r="B124" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A129" t="s">
-        <v>543</v>
+        <v>530</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A133" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>566</v>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A149" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A150" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A151" t="s">
-        <v>571</v>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>591</v>
+        <v>567</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>592</v>
+        <v>588</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A160" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A174" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A175" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A176" t="s">
-        <v>603</v>
+        <v>596</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A177" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A180" t="s">
-        <v>605</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A181" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A184" t="s">
-        <v>3</v>
+        <v>602</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>607</v>
+        <v>504</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>612</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>5</v>
+        <v>603</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>6</v>
+        <v>609</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>615</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>3</v>
+        <v>606</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>610</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>6</v>
+        <v>612</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>611</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>406</v>
+        <v>607</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>613</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>603</v>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A200" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A203" t="s">
-        <v>616</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A204" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A207" t="s">
-        <v>3</v>
+        <v>613</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>617</v>
+        <v>503</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>607</v>
+        <v>504</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>608</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>5</v>
+        <v>614</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>6</v>
+        <v>605</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>619</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>3</v>
+        <v>615</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>620</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>6</v>
+        <v>616</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>611</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>406</v>
+        <v>617</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>621</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>603</v>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A223" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A226" t="s">
-        <v>622</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A227" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A230" t="s">
-        <v>3</v>
+        <v>619</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>623</v>
+        <v>503</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>607</v>
+        <v>504</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>608</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>5</v>
+        <v>620</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>6</v>
+        <v>605</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>625</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>3</v>
+        <v>621</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>626</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>6</v>
+        <v>622</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>611</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>406</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A243" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>715</v>
+        <v>608</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A246" t="s">
-        <v>717</v>
+        <v>403</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>720</v>
+        <v>714</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A250" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>741</v>
+        <v>716</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A253" t="s">
-        <v>743</v>
+        <v>717</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A254" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>809</v>
+        <v>739</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A257" t="s">
-        <v>769</v>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A258" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A261" t="s">
-        <v>805</v>
+        <v>766</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A262" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>806</v>
+        <v>777</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A265" t="s">
-        <v>785</v>
+        <v>802</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>773</v>
+        <v>804</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A268" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A269" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A270" t="s">
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -7610,227 +7902,227 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
   </sheetData>
@@ -7922,22 +8214,22 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -8032,137 +8324,137 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K74" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K80" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -8179,127 +8471,127 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -8315,192 +8607,192 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H25" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H26" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="75" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G75" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
     </row>
     <row r="76" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G76" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -8542,47 +8834,47 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
@@ -8593,62 +8885,77 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0A0146-AD32-4B49-937B-CB2E2BCDD816}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>454</v>
+        <v>451</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -8659,22 +8966,567 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B86C8E-2C15-4C8B-856A-CBD1AA2B17B8}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A127"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>789</v>
+        <v>786</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -8690,77 +9542,77 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
@@ -8770,12 +9622,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
@@ -8785,192 +9637,192 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
   </sheetData>
@@ -8986,270 +9838,270 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B23" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
   </sheetData>
@@ -9269,52 +10121,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -9331,97 +10183,97 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
@@ -9431,12 +10283,12 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
@@ -9446,7 +10298,7 @@
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
@@ -9456,7 +10308,7 @@
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
@@ -9481,7 +10333,7 @@
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -9491,7 +10343,7 @@
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
@@ -9501,7 +10353,7 @@
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
@@ -9511,7 +10363,7 @@
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
@@ -9521,7 +10373,7 @@
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.4">
@@ -9531,42 +10383,42 @@
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
@@ -9581,57 +10433,57 @@
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F56" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F58" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F59" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F63" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F65" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F66" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F68" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="72" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F72" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F73" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F74" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
@@ -9666,7 +10518,7 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
@@ -9731,22 +10583,22 @@
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -9918,27 +10770,27 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
@@ -9948,7 +10800,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
@@ -9958,7 +10810,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
@@ -9968,7 +10820,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
@@ -9978,7 +10830,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
@@ -9988,117 +10840,117 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
@@ -10108,27 +10960,27 @@
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
@@ -10153,97 +11005,97 @@
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H107" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H108" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -10260,22 +11112,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -10301,37 +11153,37 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90954AC-C0EA-4E51-BFE5-AB09F86BC2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CF1746-3083-44C0-A100-3E3D32BCF6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="3" activeTab="9" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="926">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -1598,9 +1598,6 @@
     <t>(1)E = mc^2 // E는 에너지,m는 질량,c는 광속도</t>
   </si>
   <si>
-    <t>(1) 하는법 :</t>
-  </si>
-  <si>
     <t>3.뉴턴의 운동방정식</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3147,6 +3144,51 @@
   <si>
     <t>8. 스크립트 이름이랑 클래스 이름이 다르면 재접속</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">19.이미지 크기 맞추기 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)rect tool을 선택한채로 이미지의 꼭짓점을 잡아당기면 캔버스에 자석처럼 붙는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.콜라이더 나누기(충돌 판정 분리)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)콜라이더를 나눌 오브젝트에 empty를 추가해서 서로 겹치지 않도록 콜라이더를 배치한다 &gt; 기존오브젝트와 empty 콜라이더를 스크립트에서 따로 제어한다(side 게임 needle 참고)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20. 게임오브젝트 식별 아이콘 부여</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)인스펙터창의 이름 왼쪽부분을 클릭한후 아이콘을 선택한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 하는법 : 에디터에서 mass값 조절(rigidbody 컴퍼넌트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.rigidbody body type 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)스크립트에서 설정 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>void Start()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    rbody = GetComponent&lt;Rigidbody2D&gt;();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    rbody.bodyType = RigidbodyType2D.Static; //에디터의 바디타입(kinematic,static,dynamic)을 설정</t>
   </si>
 </sst>
 </file>
@@ -3271,1143 +3313,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>476024</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>62802</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AF8150-33B1-8A6F-2E44-14E1AEEA1CA1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7620" y="11049000"/>
-          <a:ext cx="1809524" cy="504762"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>510541</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>45637</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90BEC190-0663-E4D8-048B-6C9623A77D77}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="1752600"/>
-          <a:ext cx="1912620" cy="3596557"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>563880</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>312946</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>27013</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CBC7BF0-B43B-4DEB-B3DB-2362BDA17E0E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1905000" y="1767840"/>
-          <a:ext cx="3772426" cy="2457793"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>292450</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>11555</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8DDAA7-CD99-D281-5E58-CB47EA1BAA28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5745480"/>
-          <a:ext cx="7059010" cy="895475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>484319</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>82079</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE45E57-E895-D714-7721-01B90B01A849}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7620" y="7086600"/>
-          <a:ext cx="3219899" cy="1171739"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>23152</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>148736</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="그림 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E4F07F5-7E52-E838-5A2B-370937C82AA9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="8602980"/>
-          <a:ext cx="2095792" cy="1047896"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>286959</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>30481</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19F8FB06-D646-425C-9F5D-F0A03E4CE7E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="678180" y="12176761"/>
-          <a:ext cx="2291019" cy="3764280"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>297921</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10A8B146-6606-476F-B030-8ACFC889D355}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="678180" y="15956280"/>
-          <a:ext cx="2301981" cy="3337560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="직사각형 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02DA2E21-D818-EBD6-E544-445CC871392B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="30480" y="23660100"/>
-          <a:ext cx="3322320" cy="205740"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="직선 화살표 연결선 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D3AA7F9-98F3-0EDE-D87C-389F81D07A30}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15240" y="23644860"/>
-          <a:ext cx="4373880" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>388620</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="직선 화살표 연결선 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4366BC-962F-DA99-A73F-FB15CD0C6DC7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="30480" y="23762970"/>
-          <a:ext cx="4381500" cy="102870"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>534360</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>51900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38760</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>34320</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
-      <mc:Choice Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="15" name="잉크 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="1204920" y="23475780"/>
-            <a:ext cx="174960" cy="203400"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="15" name="잉크 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1198787" y="23469660"/>
-              <a:ext cx="187225" cy="215640"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>593400</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>9840</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>625080</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>46560</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
-      <mc:Choice Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="18" name="잉크 17">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="1263960" y="23654700"/>
-            <a:ext cx="31680" cy="36720"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="18" name="잉크 17">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1257770" y="23648580"/>
-              <a:ext cx="44061" cy="48960"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="직선 연결선 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32C3C467-3D66-B670-623E-F5BA44F74E4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1280160" y="23690580"/>
-          <a:ext cx="0" cy="182880"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="accent2"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>140</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>3054</xdr:colOff>
-      <xdr:row>150</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025F6533-138C-3EBC-2FA0-F024414B849B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="26296620"/>
-          <a:ext cx="2685294" cy="2316480"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>163</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>282541</xdr:colOff>
-      <xdr:row>175</xdr:row>
-      <xdr:rowOff>2247</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{297EE74D-2532-73BE-B9DB-137CECD3F5C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="32468820"/>
-          <a:ext cx="4305901" cy="2448267"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>287701</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>14068</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A768862A-42C9-967A-4A4C-3C100403B6DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="10386060"/>
-          <a:ext cx="6322740" cy="3107788"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="직사각형 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DAE2453-7736-B01B-488B-A53731A263DD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1912620" y="10515600"/>
-          <a:ext cx="365760" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150">
-          <a:solidFill>
-            <a:srgbClr val="C00000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>84965</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{518A2C76-B80E-BD37-8F3C-17320565FF81}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="14142721"/>
-          <a:ext cx="2118359" cy="4283584"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="직사각형 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D655B6BF-C63F-E6DE-D646-39A8B29DACD2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1851660" y="14112240"/>
-          <a:ext cx="167640" cy="167640"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>405231</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="그림 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFCD6404-0A91-63C0-9E43-93D03D205B21}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="20772120"/>
-          <a:ext cx="6440271" cy="1996440"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>7621</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>151971</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D5296B-23E3-12BC-E51E-CA3777CBBF77}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="15506700"/>
-          <a:ext cx="6713220" cy="3428571"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -5221,6 +4127,1279 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476024</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>62802</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AF8150-33B1-8A6F-2E44-14E1AEEA1CA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7620" y="11049000"/>
+          <a:ext cx="1809524" cy="504762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>510541</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45637</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90BEC190-0663-E4D8-048B-6C9623A77D77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="1752600"/>
+          <a:ext cx="1912620" cy="3596557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>312946</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>27013</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CBC7BF0-B43B-4DEB-B3DB-2362BDA17E0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1905000" y="1767840"/>
+          <a:ext cx="3772426" cy="2457793"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>292450</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>11555</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8DDAA7-CD99-D281-5E58-CB47EA1BAA28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5745480"/>
+          <a:ext cx="7059010" cy="895475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>484319</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>82079</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE45E57-E895-D714-7721-01B90B01A849}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7620" y="7086600"/>
+          <a:ext cx="3219899" cy="1171739"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>23152</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>148736</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E4F07F5-7E52-E838-5A2B-370937C82AA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8602980"/>
+          <a:ext cx="2095792" cy="1047896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>22861</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>286959</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>30481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19F8FB06-D646-425C-9F5D-F0A03E4CE7E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="678180" y="12176761"/>
+          <a:ext cx="2291019" cy="3764280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>297921</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10A8B146-6606-476F-B030-8ACFC889D355}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="678180" y="15956280"/>
+          <a:ext cx="2301981" cy="3337560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="직사각형 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02DA2E21-D818-EBD6-E544-445CC871392B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="23660100"/>
+          <a:ext cx="3322320" cy="205740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="직선 화살표 연결선 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D3AA7F9-98F3-0EDE-D87C-389F81D07A30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15240" y="23644860"/>
+          <a:ext cx="4373880" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="직선 화살표 연결선 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4366BC-962F-DA99-A73F-FB15CD0C6DC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="23762970"/>
+          <a:ext cx="4381500" cy="102870"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>534360</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>51900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38760</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>34320</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="15" name="잉크 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1204920" y="23475780"/>
+            <a:ext cx="174960" cy="203400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="15" name="잉크 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1198787" y="23469660"/>
+              <a:ext cx="187225" cy="215640"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>593400</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>9840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>625080</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>46560</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="18" name="잉크 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1263960" y="23654700"/>
+            <a:ext cx="31680" cy="36720"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="18" name="잉크 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1257770" y="23648580"/>
+              <a:ext cx="44061" cy="48960"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="직선 연결선 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32C3C467-3D66-B670-623E-F5BA44F74E4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1280160" y="23690580"/>
+          <a:ext cx="0" cy="182880"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="76200">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1658</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>67317</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4A53B53-7BD2-31E1-7C8C-96EA861A6056}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3095378"/>
+          <a:ext cx="8321040" cy="2717419"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3054</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025F6533-138C-3EBC-2FA0-F024414B849B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="26296620"/>
+          <a:ext cx="2685294" cy="2316480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>282541</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>2247</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{297EE74D-2532-73BE-B9DB-137CECD3F5C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="32468820"/>
+          <a:ext cx="4305901" cy="2448267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>287701</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>14068</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A768862A-42C9-967A-4A4C-3C100403B6DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="10386060"/>
+          <a:ext cx="6322740" cy="3107788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="직사각형 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DAE2453-7736-B01B-488B-A53731A263DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1912620" y="10515600"/>
+          <a:ext cx="365760" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>84965</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{518A2C76-B80E-BD37-8F3C-17320565FF81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="14142721"/>
+          <a:ext cx="2118359" cy="4283584"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="직사각형 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D655B6BF-C63F-E6DE-D646-39A8B29DACD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1851660" y="14112240"/>
+          <a:ext cx="167640" cy="167640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>405231</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFCD6404-0A91-63C0-9E43-93D03D205B21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20772120"/>
+          <a:ext cx="6440271" cy="1996440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>72494</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>61215</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{266A7212-6DDE-694B-BED2-0706C80E86C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="24086820"/>
+          <a:ext cx="743054" cy="1829055"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>63435</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>76641</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{502C06AB-4BDC-EDF5-E4A8-1EE802B88698}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="26746200"/>
+          <a:ext cx="4086795" cy="3162741"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>7621</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>151971</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D5296B-23E3-12BC-E51E-CA3777CBBF77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="15506700"/>
+          <a:ext cx="6713220" cy="3428571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -5730,45 +5909,45 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
+        <v>788</v>
+      </c>
+      <c r="B40" t="s">
         <v>789</v>
-      </c>
-      <c r="B40" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -5780,7 +5959,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83395862-6542-455B-8080-4B1FD46BA113}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -5850,7 +6029,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
@@ -5860,7 +6039,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
@@ -5870,12 +6049,47 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>483</v>
+        <v>920</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -6390,7 +6604,7 @@
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
@@ -6525,22 +6739,22 @@
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.4">
@@ -6550,7 +6764,7 @@
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
@@ -6560,32 +6774,32 @@
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.4">
@@ -6595,17 +6809,17 @@
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.4">
@@ -6615,17 +6829,17 @@
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.4">
@@ -6640,111 +6854,111 @@
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B181" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B184" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E184" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B185" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E185" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B186" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E186" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
@@ -6760,22 +6974,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -6791,22 +7005,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
@@ -6911,17 +7125,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
@@ -6981,35 +7195,35 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
+        <v>797</v>
+      </c>
+      <c r="G58" t="s">
         <v>798</v>
-      </c>
-      <c r="G58" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
@@ -7019,7 +7233,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
@@ -7254,7 +7468,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
@@ -7269,177 +7483,177 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B122" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B124" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.4">
@@ -7449,17 +7663,17 @@
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.4">
@@ -7469,7 +7683,7 @@
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
@@ -7479,7 +7693,7 @@
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.4">
@@ -7489,7 +7703,7 @@
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
@@ -7499,7 +7713,7 @@
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.4">
@@ -7509,42 +7723,42 @@
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
@@ -7554,17 +7768,17 @@
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.4">
@@ -7574,7 +7788,7 @@
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.4">
@@ -7584,7 +7798,7 @@
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.4">
@@ -7594,7 +7808,7 @@
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.4">
@@ -7604,7 +7818,7 @@
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.4">
@@ -7614,42 +7828,42 @@
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
@@ -7659,17 +7873,17 @@
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
@@ -7679,7 +7893,7 @@
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
@@ -7689,7 +7903,7 @@
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.4">
@@ -7699,7 +7913,7 @@
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.4">
@@ -7709,7 +7923,7 @@
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.4">
@@ -7719,102 +7933,102 @@
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
@@ -7887,7 +8101,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5B0EB0-3A18-406B-BDAC-7BBC8487A206}">
-  <dimension ref="A1:A106"/>
+  <dimension ref="A1:A121"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -7942,7 +8156,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
@@ -8027,7 +8241,7 @@
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
@@ -8057,72 +8271,92 @@
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>812</v>
+        <v>811</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>919</v>
       </c>
     </row>
   </sheetData>
@@ -8214,22 +8448,22 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -8389,72 +8623,72 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K74" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K80" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
   </sheetData>
@@ -8471,127 +8705,127 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
@@ -8657,142 +8891,142 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H26" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="75" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G75" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="76" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G76" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
   </sheetData>
@@ -8854,27 +9088,27 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -8945,17 +9179,17 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -8971,82 +9205,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
@@ -9076,12 +9310,12 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
@@ -9091,37 +9325,37 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
@@ -9131,17 +9365,17 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
@@ -9151,17 +9385,17 @@
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
@@ -9171,17 +9405,17 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
@@ -9191,42 +9425,42 @@
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
@@ -9251,77 +9485,77 @@
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
@@ -9331,27 +9565,27 @@
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
@@ -9361,7 +9595,7 @@
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
@@ -9371,7 +9605,7 @@
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
@@ -9381,7 +9615,7 @@
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
@@ -9391,7 +9625,7 @@
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
@@ -9401,7 +9635,7 @@
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
@@ -9411,7 +9645,7 @@
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
@@ -9421,7 +9655,7 @@
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
@@ -9431,7 +9665,7 @@
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
@@ -9441,7 +9675,7 @@
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
@@ -9451,7 +9685,7 @@
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.4">
@@ -9461,7 +9695,7 @@
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
@@ -9471,17 +9705,17 @@
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.4">
@@ -9491,22 +9725,22 @@
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.4">
@@ -9526,7 +9760,7 @@
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
   </sheetData>
@@ -9672,12 +9906,12 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
@@ -9692,7 +9926,7 @@
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
@@ -9822,7 +10056,7 @@
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>
@@ -9838,7 +10072,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
@@ -9941,7 +10175,7 @@
         <v>365</v>
       </c>
       <c r="B23" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
@@ -9976,132 +10210,132 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -10121,52 +10355,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>
@@ -10183,97 +10417,97 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
@@ -10283,12 +10517,12 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
@@ -10298,7 +10532,7 @@
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
@@ -10308,7 +10542,7 @@
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
@@ -10333,7 +10567,7 @@
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -10343,7 +10577,7 @@
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
@@ -10353,7 +10587,7 @@
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
@@ -10363,7 +10597,7 @@
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
@@ -10373,7 +10607,7 @@
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.4">
@@ -10383,42 +10617,42 @@
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
@@ -10438,52 +10672,52 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F56" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F58" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F59" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F63" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F65" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F66" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F68" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="72" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F72" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F73" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F74" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
@@ -10518,7 +10752,7 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
@@ -10583,22 +10817,22 @@
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -10785,12 +11019,12 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
@@ -10800,7 +11034,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
@@ -10810,7 +11044,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
@@ -10820,7 +11054,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
@@ -10830,7 +11064,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
@@ -10840,17 +11074,17 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
@@ -10920,37 +11154,37 @@
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
@@ -10960,27 +11194,27 @@
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
@@ -11005,42 +11239,42 @@
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
@@ -11050,52 +11284,52 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H107" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H108" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>
@@ -11138,7 +11372,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD10C7B-DC9E-441F-88CC-55E83D279026}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -11168,26 +11402,37 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>829</v>
+        <v>828</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CF1746-3083-44C0-A100-3E3D32BCF6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D345ED7B-C5F6-488A-AF3E-EFFE611CD9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="3" activeTab="9" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="10" activeTab="16" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="927">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -3189,6 +3189,10 @@
   </si>
   <si>
     <t xml:space="preserve">    rbody.bodyType = RigidbodyType2D.Static; //에디터의 바디타입(kinematic,static,dynamic)을 설정</t>
+  </si>
+  <si>
+    <t>17. hz의 의미 : 초당 진동 횟수(ex : 50hz면 초당 50번 진동하기 때문에 0.02초에 한번씩 진동한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8368,7 +8372,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A320F51B-952E-44A4-8797-50ACF70F49CD}">
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -8689,6 +8693,11 @@
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>825</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>926</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D345ED7B-C5F6-488A-AF3E-EFFE611CD9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC40F41-9E93-4F48-91CE-03D05076B2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="10" activeTab="16" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="9" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="842">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -426,6 +426,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>(1) 프레임 간격 사이에 경과 시간</t>
+  </si>
+  <si>
+    <t>(2)de += Time.deltaTime; //프레임간에 경과시간을 누적하여 더함.</t>
+  </si>
+  <si>
+    <t>1.time.deltaTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>2.하이러라키 창에 존재하는 게임오브젝트와 프로젝트창에 리소스는 다르다.</t>
   </si>
   <si>
@@ -1598,6 +1608,9 @@
     <t>(1)E = mc^2 // E는 에너지,m는 질량,c는 광속도</t>
   </si>
   <si>
+    <t>(1) 하는법 :</t>
+  </si>
+  <si>
     <t>3.뉴턴의 운동방정식</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2901,297 +2914,6 @@
   </si>
   <si>
     <t>(1)버튼의 이미지가 반투명해지고 상호작용이 막힌다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>using System.Collections;</t>
-  </si>
-  <si>
-    <t>using System.Collections.Generic;</t>
-  </si>
-  <si>
-    <t>public class CameraManager : MonoBehaviour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public float leftLimit = 0.0f;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public float rightLimit = 0.0f;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public float topLimit = 0.0f;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public float bottomLimit = 0.0f;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        GameObject player = GameObject.FindGameObjectWithTag("Player");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if (player != null)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Debug.Log("a");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            float x = player.transform.position.x;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            float y = player.transform.position.y;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            float z = transform.position.z;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            if (x &lt; leftLimit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                x = leftLimit;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            else if (x &gt; rightLimit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                x = rightLimit;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            if (y &lt; bottomLimit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                y = bottomLimit;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            else if (y &gt; topLimit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                y = topLimit;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Vector3 v3 = new Vector3(x, y, z);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            transform.position = v3;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public GameObject subScreen;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            if (subScreen != null)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                y = subScreen.transform.position.y;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                z = subScreen.transform.position.z;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                subScreen.transform.position = v;</t>
-  </si>
-  <si>
-    <t>(1)원리 : 카메라(먼배경)와 배경(가까운 배경)과 바닥의 속도를 달리 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)기대효과 : 실제로 기차안에서 밖을 보는것같은 원근감을 갖게 된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">                Vector3 v = new Vector3(x / 2.0f, y, z); //camera의 x좌표의 절반을 subScreen에 적용 2.0값이 속도차를 나게 하는 코드이므로 상황에 맞게 2.0값을 바꿔서 사용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. 스크립트로 구현한 추적 카메라 (limit 설정,sub screen을 이용한 입체감)(side view project 참고)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.time.deltaTime과 fixedDeltaTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)time.deltaTime : 프레임 간격 사이에 경과 시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1-2)de += Time.deltaTime; //프레임간에 경과시간을 누적하여 더함.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)fixedDeltaTime : FixedUpdate 메서드가 호출되는 간격</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. 카메라 스크롤 하는법(카메라 강제 이동)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>public bool isForceScrollX = false;</t>
-  </si>
-  <si>
-    <t>public float forceSpeedX = 0.5f;</t>
-  </si>
-  <si>
-    <t>public bool isForceScrollY = false;</t>
-  </si>
-  <si>
-    <t>public float forceSpeedY = 0.5f;</t>
-  </si>
-  <si>
-    <t>void Update()</t>
-  </si>
-  <si>
-    <t>(1)이 스크립트를 카메라한테 넣은 후 스크롤 시킬 축을 체크한다(isForceScrollX 또는 isForceScrollY)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">    GameObject player = GameObject.FindGameObjectWithTag("Player");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    if (player != null)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Debug.Log("a");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        float x = player.transform.position.x;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        float y = player.transform.position.y;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        float z = transform.position.z;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if (isForceScrollX)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            x = transform.position.x + (forceSpeedX * Time.deltaTime);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if (x &lt; leftLimit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            x = leftLimit;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        else if (x &gt; rightLimit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            x = rightLimit;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if (isForceScrollY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            y = transform.position.y + (forceSpeedY * Time.deltaTime);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if (y &lt; bottomLimit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            y = bottomLimit;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        else if (y &gt; topLimit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            y = topLimit;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vector3 v3 = new Vector3(x, y, z);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        transform.position = v3;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if (subScreen != null)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            y = subScreen.transform.position.y;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            z = subScreen.transform.position.z;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Vector3 v = new Vector3(x / 2.0f, y, z); //camera의 x좌표의 절반을 subScreen에 적용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            subScreen.transform.position = v;</t>
-  </si>
-  <si>
-    <t>public float leftLimit = 0.0f;</t>
-  </si>
-  <si>
-    <t>public float rightLimit = 0.0f;</t>
-  </si>
-  <si>
-    <t>public float topLimit = 0.0f;</t>
-  </si>
-  <si>
-    <t>public float bottomLimit = 0.0f;</t>
-  </si>
-  <si>
-    <t>4. 화면에서 벗어날 때 게임오버 시키는 법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)카메라의 자식으로 empty를 만들어서 배치한뒤 스크립트에서 tag 또는 layer(잘 사용X)로 충돌처리를 한다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2) 다른방법 : (1)의 과정에서 empty를 프리팹화 시킨뒤 프리팹화 된 empty를 배치해서 사용한다(sideview 게임 참고)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. 스크립트 이름이랑 클래스 이름이 다르면 재접속</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">19.이미지 크기 맞추기 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)rect tool을 선택한채로 이미지의 꼭짓점을 잡아당기면 캔버스에 자석처럼 붙는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.콜라이더 나누기(충돌 판정 분리)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)콜라이더를 나눌 오브젝트에 empty를 추가해서 서로 겹치지 않도록 콜라이더를 배치한다 &gt; 기존오브젝트와 empty 콜라이더를 스크립트에서 따로 제어한다(side 게임 needle 참고)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20. 게임오브젝트 식별 아이콘 부여</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)인스펙터창의 이름 왼쪽부분을 클릭한후 아이콘을 선택한다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 하는법 : 에디터에서 mass값 조절(rigidbody 컴퍼넌트)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.rigidbody body type 설정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)스크립트에서 설정 :</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>void Start()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    rbody = GetComponent&lt;Rigidbody2D&gt;();</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    rbody.bodyType = RigidbodyType2D.Static; //에디터의 바디타입(kinematic,static,dynamic)을 설정</t>
-  </si>
-  <si>
-    <t>17. hz의 의미 : 초당 진동 횟수(ex : 50hz면 초당 50번 진동하기 때문에 0.02초에 한번씩 진동한다)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3273,22 +2995,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>23673</xdr:rowOff>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>68579</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>214406</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476024</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>62802</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75B9FB04-0C01-E1DC-17BC-F96FB94BAEC7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AF8150-33B1-8A6F-2E44-14E1AEEA1CA1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3304,8 +3026,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="10188753"/>
-          <a:ext cx="6103619" cy="3063473"/>
+          <a:off x="7620" y="11049000"/>
+          <a:ext cx="1809524" cy="504762"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3317,7 +3039,1143 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>510541</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45637</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90BEC190-0663-E4D8-048B-6C9623A77D77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="1752600"/>
+          <a:ext cx="1912620" cy="3596557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>312946</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>27013</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CBC7BF0-B43B-4DEB-B3DB-2362BDA17E0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1905000" y="1767840"/>
+          <a:ext cx="3772426" cy="2457793"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>292450</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>11555</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8DDAA7-CD99-D281-5E58-CB47EA1BAA28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5745480"/>
+          <a:ext cx="7059010" cy="895475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>484319</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>82079</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE45E57-E895-D714-7721-01B90B01A849}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7620" y="7086600"/>
+          <a:ext cx="3219899" cy="1171739"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>23152</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>148736</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E4F07F5-7E52-E838-5A2B-370937C82AA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8602980"/>
+          <a:ext cx="2095792" cy="1047896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>22861</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>286959</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>30481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19F8FB06-D646-425C-9F5D-F0A03E4CE7E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="678180" y="12176761"/>
+          <a:ext cx="2291019" cy="3764280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>297921</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10A8B146-6606-476F-B030-8ACFC889D355}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="678180" y="15956280"/>
+          <a:ext cx="2301981" cy="3337560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="직사각형 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02DA2E21-D818-EBD6-E544-445CC871392B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="23660100"/>
+          <a:ext cx="3322320" cy="205740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="직선 화살표 연결선 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D3AA7F9-98F3-0EDE-D87C-389F81D07A30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15240" y="23644860"/>
+          <a:ext cx="4373880" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="직선 화살표 연결선 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4366BC-962F-DA99-A73F-FB15CD0C6DC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="23762970"/>
+          <a:ext cx="4381500" cy="102870"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>534360</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>51900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38760</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>34320</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="15" name="잉크 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1204920" y="23475780"/>
+            <a:ext cx="174960" cy="203400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="15" name="잉크 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1198787" y="23469660"/>
+              <a:ext cx="187225" cy="215640"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>593400</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>9840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>625080</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>46560</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="18" name="잉크 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1263960" y="23654700"/>
+            <a:ext cx="31680" cy="36720"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="18" name="잉크 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1257770" y="23648580"/>
+              <a:ext cx="44061" cy="48960"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="직선 연결선 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32C3C467-3D66-B670-623E-F5BA44F74E4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1280160" y="23690580"/>
+          <a:ext cx="0" cy="182880"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="76200">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>554399</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>166313</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{786F1EDB-51A5-D92F-9A7E-0E6260F878E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1341120" y="6629400"/>
+          <a:ext cx="13965599" cy="4143953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3054</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025F6533-138C-3EBC-2FA0-F024414B849B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="26296620"/>
+          <a:ext cx="2685294" cy="2316480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>282541</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>2247</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{297EE74D-2532-73BE-B9DB-137CECD3F5C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="32468820"/>
+          <a:ext cx="4305901" cy="2448267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>287701</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>14068</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A768862A-42C9-967A-4A4C-3C100403B6DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="10386060"/>
+          <a:ext cx="6322740" cy="3107788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="직사각형 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DAE2453-7736-B01B-488B-A53731A263DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1912620" y="10515600"/>
+          <a:ext cx="365760" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>84965</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{518A2C76-B80E-BD37-8F3C-17320565FF81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="14142721"/>
+          <a:ext cx="2118359" cy="4283584"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="직사각형 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D655B6BF-C63F-E6DE-D646-39A8B29DACD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1851660" y="14112240"/>
+          <a:ext cx="167640" cy="167640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>405231</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFCD6404-0A91-63C0-9E43-93D03D205B21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20772120"/>
+          <a:ext cx="6440271" cy="1996440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>7621</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>151971</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D5296B-23E3-12BC-E51E-CA3777CBBF77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="15506700"/>
+          <a:ext cx="6713220" cy="3428571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4131,1279 +4989,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>476024</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>62802</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AF8150-33B1-8A6F-2E44-14E1AEEA1CA1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7620" y="11049000"/>
-          <a:ext cx="1809524" cy="504762"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>510541</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>45637</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90BEC190-0663-E4D8-048B-6C9623A77D77}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="1752600"/>
-          <a:ext cx="1912620" cy="3596557"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>563880</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>312946</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>27013</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CBC7BF0-B43B-4DEB-B3DB-2362BDA17E0E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1905000" y="1767840"/>
-          <a:ext cx="3772426" cy="2457793"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>292450</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>11555</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8DDAA7-CD99-D281-5E58-CB47EA1BAA28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5745480"/>
-          <a:ext cx="7059010" cy="895475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>484319</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>82079</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE45E57-E895-D714-7721-01B90B01A849}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7620" y="7086600"/>
-          <a:ext cx="3219899" cy="1171739"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>23152</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>148736</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="그림 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E4F07F5-7E52-E838-5A2B-370937C82AA9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="8602980"/>
-          <a:ext cx="2095792" cy="1047896"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>286959</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>30481</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19F8FB06-D646-425C-9F5D-F0A03E4CE7E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="678180" y="12176761"/>
-          <a:ext cx="2291019" cy="3764280"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>297921</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10A8B146-6606-476F-B030-8ACFC889D355}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="678180" y="15956280"/>
-          <a:ext cx="2301981" cy="3337560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="직사각형 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02DA2E21-D818-EBD6-E544-445CC871392B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="30480" y="23660100"/>
-          <a:ext cx="3322320" cy="205740"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="직선 화살표 연결선 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D3AA7F9-98F3-0EDE-D87C-389F81D07A30}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15240" y="23644860"/>
-          <a:ext cx="4373880" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>388620</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="직선 화살표 연결선 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4366BC-962F-DA99-A73F-FB15CD0C6DC7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="30480" y="23762970"/>
-          <a:ext cx="4381500" cy="102870"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>534360</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>51900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38760</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>34320</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
-      <mc:Choice Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="15" name="잉크 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="1204920" y="23475780"/>
-            <a:ext cx="174960" cy="203400"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="15" name="잉크 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93889D32-DA49-8AD8-E62F-C38EED629698}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1198787" y="23469660"/>
-              <a:ext cx="187225" cy="215640"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>593400</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>9840</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>625080</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>46560</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
-      <mc:Choice Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="18" name="잉크 17">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="1263960" y="23654700"/>
-            <a:ext cx="31680" cy="36720"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="18" name="잉크 17">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD01BA2-D839-9B73-4E0A-D8F8027A26CF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1257770" y="23648580"/>
-              <a:ext cx="44061" cy="48960"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="직선 연결선 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32C3C467-3D66-B670-623E-F5BA44F74E4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1280160" y="23690580"/>
-          <a:ext cx="0" cy="182880"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="accent2"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>1658</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>67317</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4A53B53-7BD2-31E1-7C8C-96EA861A6056}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3095378"/>
-          <a:ext cx="8321040" cy="2717419"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>140</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>3054</xdr:colOff>
-      <xdr:row>150</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025F6533-138C-3EBC-2FA0-F024414B849B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="26296620"/>
-          <a:ext cx="2685294" cy="2316480"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>163</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>282541</xdr:colOff>
-      <xdr:row>175</xdr:row>
-      <xdr:rowOff>2247</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{297EE74D-2532-73BE-B9DB-137CECD3F5C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="32468820"/>
-          <a:ext cx="4305901" cy="2448267"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>287701</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>14068</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A768862A-42C9-967A-4A4C-3C100403B6DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="10386060"/>
-          <a:ext cx="6322740" cy="3107788"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="직사각형 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DAE2453-7736-B01B-488B-A53731A263DD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1912620" y="10515600"/>
-          <a:ext cx="365760" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150">
-          <a:solidFill>
-            <a:srgbClr val="C00000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>84965</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{518A2C76-B80E-BD37-8F3C-17320565FF81}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="14142721"/>
-          <a:ext cx="2118359" cy="4283584"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="직사각형 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D655B6BF-C63F-E6DE-D646-39A8B29DACD2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1851660" y="14112240"/>
-          <a:ext cx="167640" cy="167640"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>405231</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="그림 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFCD6404-0A91-63C0-9E43-93D03D205B21}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="20772120"/>
-          <a:ext cx="6440271" cy="1996440"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>72494</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>61215</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="그림 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{266A7212-6DDE-694B-BED2-0706C80E86C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="24086820"/>
-          <a:ext cx="743054" cy="1829055"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>63435</xdr:colOff>
-      <xdr:row>135</xdr:row>
-      <xdr:rowOff>76641</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="그림 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{502C06AB-4BDC-EDF5-E4A8-1EE802B88698}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="26746200"/>
-          <a:ext cx="4086795" cy="3162741"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>7621</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>151971</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D5296B-23E3-12BC-E51E-CA3777CBBF77}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="15506700"/>
-          <a:ext cx="6713220" cy="3428571"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -5760,7 +5345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B5B9BE-0D1B-456B-B9E1-2DF1026954E4}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -5780,22 +5365,22 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
@@ -5805,7 +5390,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
@@ -5815,57 +5400,57 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -5873,97 +5458,91 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B40" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>913</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83395862-6542-455B-8080-4B1FD46BA113}">
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -6018,87 +5597,53 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>403</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6109,27 +5654,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -6250,277 +5795,277 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
@@ -6528,27 +6073,27 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B94" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
@@ -6558,207 +6103,207 @@
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.4">
@@ -6768,7 +6313,7 @@
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
@@ -6778,32 +6323,32 @@
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.4">
@@ -6813,42 +6358,42 @@
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.4">
@@ -6858,111 +6403,111 @@
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B181" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B184" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="E184" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B185" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="E185" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B186" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E186" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -6978,22 +6523,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -7004,1035 +6549,1030 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194DBF29-D361-403B-8094-6B4DBAD9B202}">
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>870</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>871</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>873</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>209</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>208</v>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>222</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>223</v>
+        <v>524</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>224</v>
+        <v>526</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>523</v>
+        <v>527</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>230</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>247</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>250</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>251</v>
+        <v>796</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>797</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>499</v>
+        <v>801</v>
+      </c>
+      <c r="G55" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>794</v>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>797</v>
-      </c>
-      <c r="G58" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>795</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A62" t="s">
-        <v>6</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>403</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>253</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A73" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>305</v>
+        <v>379</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A80" t="s">
-        <v>376</v>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>379</v>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>387</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>388</v>
+        <v>289</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>389</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>408</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>289</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>395</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>396</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>400</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A114" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>596</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>403</v>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A119" t="s">
-        <v>475</v>
+      <c r="B119" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>476</v>
+        <v>597</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A121" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B122" t="s">
-        <v>589</v>
+      <c r="B121" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>593</v>
+        <v>531</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B124" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A126" t="s">
-        <v>527</v>
+      <c r="A124" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>528</v>
+        <v>555</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A130" t="s">
-        <v>551</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>539</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A135" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A139" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A140" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A152" t="s">
-        <v>565</v>
+        <v>568</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>567</v>
+        <v>588</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A157" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>588</v>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A162" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A163" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A164" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A177" t="s">
-        <v>610</v>
+        <v>601</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A174" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A175" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A176" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A181" t="s">
-        <v>600</v>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A180" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>601</v>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A184" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>502</v>
+        <v>606</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>503</v>
+        <v>607</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>3</v>
+        <v>612</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>602</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>608</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>5</v>
+        <v>615</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>605</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>6</v>
+        <v>610</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>611</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>3</v>
+        <v>611</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>606</v>
+        <v>406</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>6</v>
+        <v>613</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A200" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A204" t="s">
-        <v>600</v>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A203" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>612</v>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A207" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>502</v>
+        <v>617</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>503</v>
+        <v>607</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>3</v>
+        <v>608</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>613</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>604</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>5</v>
+        <v>619</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>614</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>6</v>
+        <v>620</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>615</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>3</v>
+        <v>611</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>616</v>
+        <v>406</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>6</v>
+        <v>621</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A223" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A227" t="s">
-        <v>600</v>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A226" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>618</v>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>502</v>
+        <v>623</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>503</v>
+        <v>607</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>3</v>
+        <v>608</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>619</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>604</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>5</v>
+        <v>625</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>620</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>6</v>
+        <v>626</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>621</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>3</v>
+        <v>611</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A243" t="s">
-        <v>6</v>
+        <v>406</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>607</v>
+        <v>715</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>403</v>
+        <v>716</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A246" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A250" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>715</v>
+        <v>741</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A254" t="s">
-        <v>737</v>
+        <v>742</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A253" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>738</v>
+        <v>809</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A258" t="s">
-        <v>805</v>
+        <v>803</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A257" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A262" t="s">
-        <v>800</v>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A261" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>776</v>
+        <v>806</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>801</v>
+        <v>807</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A265" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A268" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A269" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A270" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -8105,7 +7645,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5B0EB0-3A18-406B-BDAC-7BBC8487A206}">
-  <dimension ref="A1:A121"/>
+  <dimension ref="A1:A106"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -8120,247 +7660,227 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A120" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A121" t="s">
-        <v>919</v>
+        <v>815</v>
       </c>
     </row>
   </sheetData>
@@ -8372,7 +7892,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A320F51B-952E-44A4-8797-50ACF70F49CD}">
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -8452,22 +7972,22 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -8562,142 +8082,137 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K74" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K80" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>926</v>
+        <v>829</v>
       </c>
     </row>
   </sheetData>
@@ -8714,127 +8229,127 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -8850,192 +8365,192 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H25" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H26" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="75" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G75" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
     </row>
     <row r="76" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G76" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -9077,47 +8592,47 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -9128,77 +8643,62 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0A0146-AD32-4B49-937B-CB2E2BCDD816}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>912</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -9209,567 +8709,22 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B86C8E-2C15-4C8B-856A-CBD1AA2B17B8}">
-  <dimension ref="A1:A127"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A55" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A56" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A58" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A62" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A63" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A66" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A67" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A70" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A72" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A73" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A74" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A75" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A82" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A83" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A84" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A85" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A86" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A87" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A88" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A90" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A91" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A92" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A93" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A94" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A96" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A101" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A114" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A115" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A116" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A117" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A118" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A119" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A120" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A121" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A122" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A124" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A125" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A127" t="s">
-        <v>880</v>
+        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -9785,77 +8740,77 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
@@ -9865,12 +8820,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
@@ -9880,192 +8835,192 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -10081,270 +9036,270 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B23" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>
@@ -10364,52 +9319,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
   </sheetData>
@@ -10426,97 +9381,97 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
@@ -10526,12 +9481,12 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
@@ -10541,7 +9496,7 @@
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
@@ -10551,7 +9506,7 @@
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
@@ -10576,7 +9531,7 @@
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -10586,7 +9541,7 @@
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
@@ -10596,7 +9551,7 @@
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
@@ -10606,7 +9561,7 @@
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
@@ -10616,7 +9571,7 @@
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.4">
@@ -10626,42 +9581,42 @@
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
@@ -10676,57 +9631,57 @@
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F56" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F58" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F59" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F63" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F65" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F66" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F68" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="72" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F72" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F73" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F74" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
@@ -10761,7 +9716,7 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
@@ -10826,22 +9781,22 @@
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -11013,27 +9968,27 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
@@ -11043,7 +9998,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
@@ -11053,7 +10008,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
@@ -11063,7 +10018,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
@@ -11073,7 +10028,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
@@ -11083,117 +10038,117 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
@@ -11203,27 +10158,27 @@
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
@@ -11248,97 +10203,97 @@
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H107" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H108" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -11355,22 +10310,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -11381,7 +10336,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD10C7B-DC9E-441F-88CC-55E83D279026}">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -11396,52 +10351,41 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>917</v>
+        <v>832</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC40F41-9E93-4F48-91CE-03D05076B2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299A4231-C226-4E14-ADA6-445A7D2C00F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="9" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="6" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="844">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -2914,6 +2914,14 @@
   </si>
   <si>
     <t>(1)버튼의 이미지가 반투명해지고 상호작용이 막힌다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11. evnetTrigger의 pointDown vs onClick() 차이점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포인터 다운은 누를때 실행되기 때문에 홀드를 해도 누르자마자 실행된다. 반면에 온클릭은 홀드를 하고 있을때 버튼에서 손을 때야 실행됨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9808,7 +9816,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22FACE01-8634-40CF-BA9C-3264EEAD61A5}">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -10294,6 +10302,16 @@
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>841</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>843</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299A4231-C226-4E14-ADA6-445A7D2C00F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FA8C92-8D05-41D1-AFC3-B43B7080DF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="6" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="11" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -1863,10 +1863,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(2)식기반 프로퍼티 : private으로 필드를 만들어주고 단, get만 가능하다. Set기능이 없음 private 필드를 보호하기 위해서 set을 사용하지 못한다.(일반프로퍼티와 사용용도가 다름)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(3)자동구현 프로퍼티</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2922,6 +2918,10 @@
   </si>
   <si>
     <t>포인터 다운은 누를때 실행되기 때문에 홀드를 해도 누르자마자 실행된다. 반면에 온클릭은 홀드를 하고 있을때 버튼에서 손을 때야 실행됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)식기반 프로퍼티 : private으로 필드를 만들어주고 단, get만 가능하다. Set기능이 없음 private 필드를 보호하기 위해서 set을 사용하지 못한다.(필드값이 수정이 되면 안돼는(보호가 필요한 필드)보호 차원에서 사용X)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5506,40 +5506,40 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
+        <v>791</v>
+      </c>
+      <c r="B40" t="s">
         <v>792</v>
-      </c>
-      <c r="B40" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
@@ -6296,12 +6296,12 @@
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
@@ -6411,7 +6411,7 @@
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>558</v>
+        <v>843</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.4">
@@ -6426,96 +6426,96 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B181" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B184" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E184" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B185" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E185" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B186" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E186" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -6747,12 +6747,12 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
@@ -6762,20 +6762,20 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
+        <v>800</v>
+      </c>
+      <c r="G55" t="s">
         <v>801</v>
-      </c>
-      <c r="G55" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
@@ -6785,7 +6785,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
@@ -7020,7 +7020,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
@@ -7035,22 +7035,22 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B119" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B121" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
@@ -7085,107 +7085,107 @@
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.4">
@@ -7195,7 +7195,7 @@
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.4">
@@ -7215,17 +7215,17 @@
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.4">
@@ -7235,7 +7235,7 @@
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.4">
@@ -7245,7 +7245,7 @@
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.4">
@@ -7255,7 +7255,7 @@
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
@@ -7265,7 +7265,7 @@
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
@@ -7275,22 +7275,22 @@
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.4">
@@ -7300,7 +7300,7 @@
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.4">
@@ -7320,17 +7320,17 @@
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.4">
@@ -7340,7 +7340,7 @@
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.4">
@@ -7350,7 +7350,7 @@
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.4">
@@ -7360,7 +7360,7 @@
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.4">
@@ -7370,7 +7370,7 @@
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.4">
@@ -7380,22 +7380,22 @@
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.4">
@@ -7405,7 +7405,7 @@
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
@@ -7425,17 +7425,17 @@
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
@@ -7445,7 +7445,7 @@
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
@@ -7455,7 +7455,7 @@
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.4">
@@ -7465,7 +7465,7 @@
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.4">
@@ -7475,7 +7475,7 @@
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.4">
@@ -7485,102 +7485,102 @@
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -7708,7 +7708,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
@@ -7843,52 +7843,52 @@
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -8165,62 +8165,62 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K74" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="K80" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -8237,127 +8237,127 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -8438,127 +8438,127 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H25" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H26" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="75" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G75" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="76" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G76" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -8620,27 +8620,27 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
@@ -8722,17 +8722,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
   </sheetData>
@@ -9028,7 +9028,7 @@
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -9044,7 +9044,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
@@ -9147,7 +9147,7 @@
         <v>368</v>
       </c>
       <c r="B23" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
@@ -9182,132 +9182,132 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -9327,52 +9327,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -9389,82 +9389,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
@@ -9489,12 +9489,12 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
@@ -9504,7 +9504,7 @@
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
@@ -9514,7 +9514,7 @@
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
@@ -9539,7 +9539,7 @@
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -9549,7 +9549,7 @@
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
@@ -9559,7 +9559,7 @@
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
@@ -9569,7 +9569,7 @@
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
@@ -9579,7 +9579,7 @@
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.4">
@@ -9589,42 +9589,42 @@
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
@@ -9644,52 +9644,52 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F56" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F58" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F59" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="F63" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F65" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F66" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F68" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="72" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F72" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F73" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F74" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
@@ -9789,12 +9789,12 @@
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
@@ -9804,7 +9804,7 @@
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -9991,12 +9991,12 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
@@ -10006,7 +10006,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
@@ -10016,7 +10016,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
@@ -10026,7 +10026,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
@@ -10036,7 +10036,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
@@ -10046,17 +10046,17 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
@@ -10256,62 +10256,62 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H107" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
       <c r="H108" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -10384,22 +10384,22 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FA8C92-8D05-41D1-AFC3-B43B7080DF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D977251E-A771-41AE-B327-3A80CB6D2D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="11" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="2" activeTab="4" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="850">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -2922,6 +2922,30 @@
   </si>
   <si>
     <t>(2)식기반 프로퍼티 : private으로 필드를 만들어주고 단, get만 가능하다. Set기능이 없음 private 필드를 보호하기 위해서 set을 사용하지 못한다.(필드값이 수정이 되면 안돼는(보호가 필요한 필드)보호 차원에서 사용X)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.타일맵 콜라이더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>none : 콜라이더 X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sprite : 콜라이더 O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-3 콜라이더 분리 시키는 법 : Grid를 선택 &gt; 우클릭 해서 새로운 타일맵 추가 &gt; 팔레트를 꺼낸 후 새로 추가된 타일맵을 선택한 채로 타일을 찍음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-1 적용 : 하이러라키창에서 grid의 자식인 tilemap을 선택 &gt; tilemap collider 2D 컴퍼넌트 추가 &gt; 그 후 프로젝트 창에서 팔레트에 등록된 타일맵을 선택 &gt; collider type을 지정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">5-2 collider type 종류 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3261,6 +3285,50 @@
         <a:xfrm>
           <a:off x="0" y="8602980"/>
           <a:ext cx="2095792" cy="1047896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>216580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>655321</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>138427</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{600A2C70-4A54-EF9D-68E1-9B92DA781C1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="10602640"/>
+          <a:ext cx="4739640" cy="1910667"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9319,7 +9387,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1A77090-18B0-472F-8043-B4280C2A82C4}">
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.59765625" bestFit="1" customWidth="1"/>
@@ -9373,6 +9441,36 @@
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>738</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>847</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282719F6-F5B6-4F9E-B9E8-0D000D817B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B038759-549D-4DE2-804A-D13D216A9371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="970" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="970" firstSheet="6" activeTab="13" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="892">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -144,9 +144,6 @@
     <t>(1) 인터넷연결과 무관하다.</t>
   </si>
   <si>
-    <t xml:space="preserve">(3)변수와 다르게 게임실행이 종료되더라도 메모리에서 사라지지 않는다. </t>
-  </si>
-  <si>
     <t xml:space="preserve">로칼에 저장하기 </t>
   </si>
   <si>
@@ -276,9 +273,6 @@
     <t xml:space="preserve">        }  // C#용 코드</t>
   </si>
   <si>
-    <t>1. Ray 형 오브젝트</t>
-  </si>
-  <si>
     <t>2.Raycast 메소드</t>
   </si>
   <si>
@@ -307,9 +301,6 @@
     <t>(1) RaycastHit은 Ray와 원점이 충돌한 지점의 정보를 가지고 있는 구조체 자료형</t>
   </si>
   <si>
-    <t xml:space="preserve">(2)세번째 매개변수 인자는 카메라와 닿는 물체사이의 거리를 구해서 설정해준다. </t>
-  </si>
-  <si>
     <t>5. 코드 분석법</t>
   </si>
   <si>
@@ -346,9 +337,6 @@
     <t>1.OnTriggerEnter 메소드</t>
   </si>
   <si>
-    <t>(1)매개변수 other의 의미 : 충돌한 상대 오브젝트.</t>
-  </si>
-  <si>
     <t>(1) 의미 : 스크립트에서 오브젝트를 식별하기 위한 수단</t>
   </si>
   <si>
@@ -379,9 +367,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1)public(프로퍼티의 set,get의 기본 접근 지정자)</t>
-  </si>
-  <si>
     <t>(2)private(attr(필드,메소드,프로퍼티)의 기본 접근지정자)</t>
   </si>
   <si>
@@ -429,12 +414,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1) 기능 : 스크립트상에서 오브젝트의 컴포넌트를 추가해준다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2) 사용법 : gameObject.AddComponent(typeof(SphereCollider)); </t>
-  </si>
-  <si>
     <t>(3) 잘못된 사용법 : gameObject.AddComponent( "SphereCollider" ) as SphereCollider; // 비추천 방식, 에러 가능성 있음(deprecated)</t>
   </si>
   <si>
@@ -819,9 +798,6 @@
     <t>(3)PlayerPrefs file 위치 : 윈도우 아이콘 우클릭 -&gt; 실행 -&gt; regedit 엔터 -&gt; HKEY_CURRENT_USER -&gt; Software -&gt; [company name] (만약 안적었다면 DefaultCompany) -&gt; [product name] (키값 이름 찾기)</t>
   </si>
   <si>
-    <t>텍스트로 저장이 아니라 바이너리(이진수)로 저장되어 있음.</t>
-  </si>
-  <si>
     <t>9.PlayerPrefs</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -852,10 +828,6 @@
     <t>defalt로 설정이 된다 따라서 UI용으로 사용하려면 수동으로 Spirte 타입으로 변경해야 한다.</t>
   </si>
   <si>
-    <t>6. 3차원 프로젝트에서 2d ui요소를 만들때 이미지 파일이 연결이 잘 안될때</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(1) dodge 프로젝트 PlayerCotroller.cs 참고</t>
   </si>
   <si>
@@ -881,10 +853,6 @@
     <t>문제 발생(speed 값이 8로 했더니 이상했고 50정도로 했더니 해결됨)</t>
   </si>
   <si>
-    <t>10.mathf.clamp(float value,float min,float max)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(1)의미 : 크기 + 방향을 두가지 물리량을 가지고 있음 (예: 속도,가속도,무게,힘...)</t>
   </si>
   <si>
@@ -1190,9 +1158,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1)리턴값없이 함수를 종료하는역할 : if문의 바디안에서 함수를 종료해야할 필요가 있을때 리턴을 써야 함수가 끝남.</t>
-  </si>
-  <si>
     <t>14.return()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1225,12 +1190,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1)의미 : 충돌할때 생기는 배열</t>
-  </si>
-  <si>
-    <t>(2)배열의 인덱스로 0번을 주로 쓴다 왜냐하면 현실적으로 동시에 두개이상의 충돌포인트를 갖는게 힘들기 때문이다.</t>
-  </si>
-  <si>
     <t>(3)ex ) private void OnCollisionEnter2D(Collision2D collision) {</t>
   </si>
   <si>
@@ -1287,16 +1246,10 @@
     <t>(1)주의사항 : 2D프로젝트에서는 콜백안됨.</t>
   </si>
   <si>
-    <t>(2)2D프로젝트에선 2D형 컴퍼넌트,메소드를 사용할것 예외는 vector3</t>
-  </si>
-  <si>
     <t>2.OnCollisionEnter()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1)SortingLayer로 정렬하기 : Sprite Renderer 컴퍼넌트 -&gt; Sorting Layer -&gt; Add Sorting Layer -&gt; +버튼클릭 -&gt; Layer추가(숫자가 높을수록 앞에 있고 낮을수록 가려진다) -&gt;각 오브젝트 선택후Sorting Layer값선택</t>
-  </si>
-  <si>
     <t>11.레이어로 정렬하기(오브젝트들이 화면에 겹쳐지는 순서)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1370,9 +1323,6 @@
     <t>-&gt; 객체의 getter 구현( public static Store getInstance() {return instance}</t>
   </si>
   <si>
-    <t>(3)유니티에서 싱글톤 만드는법 :</t>
-  </si>
-  <si>
     <t>16.싱글톤(single tone)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1380,21 +1330,12 @@
     <t>(1)추상클래스는 추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)를 가지고있는 클래스</t>
   </si>
   <si>
-    <t>(2)추상클래스를 상속한 자식클래스에서 그 추상메소드를 오버라이딩해서 추상메소드를 사용할 수 있는 메소드로 만든다.(구현) extends사용</t>
-  </si>
-  <si>
-    <t>(3)단,  자식클래스에서 추상클래스의 추상메소드를 오버라이딩 할 의무는 없다(선택이다  extends 사용)</t>
-  </si>
-  <si>
     <t>(1)상수,추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)만 가지고있는 클래스 필드,일반메소드는 존재할 수 없음.</t>
   </si>
   <si>
     <t>(2)자식인터페이스에서 상속 가능(extends) 자식인터페이스끼리 상속</t>
   </si>
   <si>
-    <t>(3)자식클래스에서 상속하는경우 반드시 추상클래스의 추상메소드를 의무적으로 구현해줘야함(implements 사용)</t>
-  </si>
-  <si>
     <t xml:space="preserve">(4)추상클래스와의 차이점 : 추상메소드의 구현을 자식클래스에서 강제적으로 하면 인터페이스, 선택이면 추상클래스 이다. 그리고 추상클래스와 인터페이스는 공통적으로 다형성(오버라이딩,오버로딩) 구현의 수단이다. </t>
   </si>
   <si>
@@ -1494,12 +1435,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1)setActive는 GameObject클래스 소속의 메소드고 GameObject클래스 + 상속한 자식클래스의 참조변수에서만 사용할 수 있다. 따라서 GameObject와 상속관계가 없는 Component형 참조변수(예 : TraillRenderer)를 통해서는 호출 할 수 없다</t>
-  </si>
-  <si>
-    <t>(2)따라서 Component형 참조변수를 활성화시키거나 비활성화 시킬때는 SetActive를 사용할 수 없고, Component클래스에서 제공하는 enabled 프로퍼티를 사용해서 활성화,비활성화 처리를 할 수있다.</t>
-  </si>
-  <si>
     <t>21.메소드의 동작방식(동기식,비동기식)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1549,9 +1484,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1)게임오브젝트 : 유니티 내에서 사용하는 고유 좌표계</t>
-  </si>
-  <si>
     <t>(2) UI : 스크린좌표계(픽셀)</t>
   </si>
   <si>
@@ -1637,10 +1569,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">(4)gameObject.Find() : 게임오브젝트만 찾아준다. 그리고 비활성 상태의 오브젝트는 못찾는다. 비활성화된 오브젝트를 찾는방법은 여러가지가 있지만 가장 간단한건 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스크립트코드에서 public GameObject 형 필드를 만들고 에디터에서 해당 비활성 오브젝트를 드래그해서 연결해준다.(유니런에서 사용한 방법)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1892,10 +1820,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>반대로 참조변수의 자료형이 Component형 또는 자식형이면 enabled를 사용 할 수있지만 SetActive는 접근할 수 없다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(3)사용법 : 오브젝트 자체를 활성화시키거나 비활성화 시킬때에는 SetActive를 사용한다. 단, SetActive를 사용하면 해당오브젝트소속의 오브젝트가 동시에 활성화되거나 비활성화된다. 만약</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1904,10 +1828,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">(4)어차피  두개의 소속클래스가 다르기때문에 참조변수의 자료형이 GameObject형 또는 자식형이면 SetActive는 사용할 수 있지만 enabled는 접근 할 수 없다. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(1)의미 : 유니티 이벤트 인스턴스를 참조하는 자료형</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2144,30 +2064,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>26. UGUI프로젝트의 Loading.cs코드에서 UI요소 슬라이더를 GameObject형으로도 받고 동시에 Slider형으로도 받는 이유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)UI요소인 Slider는 기본적으로 Slider형이다. 하지만 그 UI가 Scene에 포함되는 순간 그Slider UI는 Slider형이면서 GameObjcect형도 가능하다(만약 Slider UI가 Scene에 포함되어있지않다면 GameObject가 아니다. Slider형이다)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(3)UGUI프로젝트의 Slider는 Slider형이면서 GameObject형인 상태인데 Loading.cs코드내에서 Slider에 대해 SetActive()메소드를 호출할 필요성이 있는데 SetActive()메소드는 GameObject클래스 메소드 이므로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> GameObject형 참조변수를 통해서 호출해야한다. 그리고 value라는 프로퍼티를 사용해서 그 Slider의 값을 설정해줘야하는데 value라는 프로퍼티는 Slider소속의 프로퍼티이므로 Slider형 참조변수를 통해서 호출해야 한다. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>만약 GameObject클래스와 Slider클래스간의 상속관계가 존재한다면 둘중의 자식형 자료형만으로 선언하면 SetActive()메소드와 value프로퍼티를 사용할 수 있을수 있겠지만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안타깝게도 GameObject클래스와 Slider클래스간의 상속관계가 없기  때문에 따로 자료형 2가지로 선언할수 밖에 없는 것이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(3)주의 : unityEvent클래스 소속의 동명의 Invoke메소드와 완전히 다른 메소드임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2208,10 +2104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(4-5)yield return StartCoroutiune(string형 매개변수) : 입력한 다른 코루틴이 끝날 떄까지 대기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(5)yield break : 코루틴이 종료되고 메인루틴만 처리되는 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2493,10 +2385,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(4-1)주의사항 : 부모뼈대 의해서 자식뼈대가 종속되는 것은 애니메이션 동작이 종속되는 것이지 transform(이동,회전)이 종속되는것이 아니다 transform의 종속관계는 뼈대의 부자관계하고는 아무 관계 없다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>transform의 종속관계는 하이러라키창에서 그거와 관련있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2549,9 +2437,6 @@
     <t xml:space="preserve">     // 오브젝트를 endPos 방향으로 이동</t>
   </si>
   <si>
-    <t xml:space="preserve">     //MoveTowards 메소드의 정의 : 첫번째 매개변수는 시작점, 두번째 매개변수가 방향,세번째 매개변수 호출될때 마다의 이동량</t>
-  </si>
-  <si>
     <t xml:space="preserve">     transform.position = Vector3.MoveTowards(transform.position, endPos, moveSpeed * Time.deltaTime);</t>
   </si>
   <si>
@@ -2659,10 +2544,6 @@
     <t xml:space="preserve">     </t>
   </si>
   <si>
-    <t>24.프리팹 안에 있는 머터리얼에 접근해야 할때 : sharedMaterial을 사용(Material 사용불가) 자세한 내용은 dodge 동아리용 참고(Bullet Controller)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>15. 2차원에서 콜라이더 변형시키기 : 변형시키려는 게임오브젝트의 콜라이더를 polygon collider 2D로 넣은뒤, Edit collider 버튼을 누른다 &gt; 마우스 포인터를 활용해 조정한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2743,10 +2624,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1) Friction : 마찰계수(0이면 없고 1이면 최대)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(3)만드는법 : 프로젝트 &gt; 2D &gt; physics material 2D</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2791,10 +2668,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>포인터 다운은 누를때 실행되기 때문에 홀드를 해도 누르자마자 실행된다. 반면에 온클릭은 홀드를 하고 있을때 버튼에서 손을 때야 실행됨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(2)식기반 프로퍼티 : private으로 필드를 만들어주고 단, get만 가능하다. Set기능이 없음 private 필드를 보호하기 위해서 set을 사용하지 못한다.(필드값이 수정이 되면 안돼는(보호가 필요한 필드)보호 차원에서 사용X)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2823,14 +2696,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(1)두개를 따로 받는 이유 : UI 요소(Slider, Button 등)는 GameObject가 아니라 그 위에 붙는 Component다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>따라서 슬라이더 오브젝트를 끄고 싶다면 변수를 두 개 만들 필요 없이, mySlider.gameObject.SetActive(false); 처럼 컴포넌트가 소속된 본체(gameObject 프로퍼티)에 접근해서 꺼야 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(1) Ray 자체는 시작점과 방향만 있는 수학적 선이므로 콜라이더나 리지드바디를 가지지 않는다. 하지만 Physics.Raycast로 무언가를 감지해 내려면, 맞는 대상(오브젝트)에는 반드시 콜라이더가 있어야 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3027,43 +2892,6 @@
   </si>
   <si>
     <t>즉 Audio Listener컴퍼넌트가 비활성화 되면 Scene내에서 발생하는 소리를 녹음할 수 없기 때문에 게임시작시 아무소리도 안들리게 된다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1) 생성 시점이 아니라, 게임이 실행될 때(Play 버튼 클릭 직후) 또는 Instantiate()를 통해 스크립트가 포함된 오브젝트가 씬에 활성화(생성)되는 순간 최초 1회 호출되는 초기화 함수. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">직접 호출은 불가하지만, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>컴포넌트변수명.gameObject.SetActive(true/false)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 형식으로 컴포넌트가 부착된 본체 게임오브젝트의 활성화 상태를 언제든지 제어할 수 있다</t>
-    </r>
-  </si>
-  <si>
-    <t>(1)클래스 : 인스턴스가 heap영역에 저장되고 구조체의 데이터는 변수공간에 직접 저장됨 구조체는 가비지 컬렉션이 필요없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구조체는 값 타입(Value Type)으로 주로 스택(Stack) 메모리에 할당되며, 해당 스코프(함수 블록 등)를 벗어나면 C# 런타임(CLR)이 스택 프레임을 비우면서 자동으로 메모리가 해제된다.</t>
   </si>
   <si>
     <r>
@@ -3374,10 +3202,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Mathf.Infinity를 사용하는 것은 코딩할 땐 편하지만, 실무 최적화 관점에서는 물리 엔진이 씬 내의 모든 콜라이더를 끝까지 뚫고 연산하려 시도하기 때문에 성능 낭비가 심하다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>거리 제한은 가급적 필요한 만큼만(예: 100f 등) 설정하고, 4번째 매개변수인 레이어 마스크(LayerMask)를 활용해 특정 레이어만 충돌 검사하도록 해야한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3417,6 +3241,274 @@
       <t>를 사용해야 불필요한 string 가비지(Garbage)가 생성되지 않는다</t>
     </r>
   </si>
+  <si>
+    <t>(2)세 번째 매개변수(maxDistance)는 '레이저를 얼마나 멀리 쏠 것인가(최대 탐지 사거리)'를 개발자가 직접 정해주는 값이다. (물체와의 실제 거리는 충돌 후 hit.distance로 알아냄)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Ray 형 구조체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4-5)yield return StartCoroutine(string형 매개변수) : 입력한 다른 코루틴이 끝날 떄까지 대기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">반복문(while) 안에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>new WaitForSeconds()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">를 계속 호출하면 메모리 쓰레기(Garbage)가 발생해 렉을 유발하므로, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자주 쓰는 대기 시간은 변수에 미리 캐싱(저장)해 두고 재사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하는 것이 실전 최적화 기법이다.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">6. 3차원 프로젝트에서 2d ui요소를 만들때 이미지 파일이 연결이 잘 안될때 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)public(C# 클래스 멤버의 기본 접근 지정자는 public이 아니라 private이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)매개변수 other의 의미 : 충돌한 상대 오브젝트의 Collider(또는 Collider2D) 컴포넌트. (오브젝트 자체를 제어하려면 other.gameObject로 접근해야 함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)2D 프로젝트에서는 2D 전용인 OnCollisionEnter2D()를 사용해야 함. (2) 2D 물리 연산(Velocity, AddForce)에는 가급적 Vector3가 아닌 Vector2를 사용하는 것이 원칙.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) Friction : 마찰계수 (0이면 미끄러움. 1이 최대가 아니며 2.0, 5.0 등 1 이상으로 설정하여 더 끈끈한 벽이나 경사면을 만들 수 있음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mathf.Infinity를 사용하는 것은 코딩할 땐 편하지만, 불필요하게 먼 거리까지 물리 연산을 시도하므로 낭비가 생길 수 있다. (단, 모든 물체를 관통하며 검사하는 것은 아니며 가장 먼저 닿은 물체를 찾으면 연산이 종료됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">     //MoveTowards 메소드의 정의 : 첫번째 매개변수는 시작점, 두번째 매개변수가 도착점(목표 좌표), 세번째 매개변수 호출될때 마다의 이동량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)변수와 다르게 게임실행이 종료되더라도 스토리지(기기 내부 저장소, 하드디스크 등)에 파일이나 레지스트리 형태로 기록되므로 데이터가 영구적으로 보존된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-1) Any state : 화살표 조건만 만족하면 연결된 상태로 바로 바뀜. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단, 인스펙터에서 'Can Transition To Self(자기 자신으로 전이)' 체크를 해제해야 함. (체크 시 조건이 만족되는 동안 매 프레임 자기 자신으로 무한 전환(리셋)되어 애니메이션이 굳어있는 것처럼 보이기 때문)</t>
+  </si>
+  <si>
+    <t>(2) 컴포넌트 참조 변수를 통해서도 '참조변수.gameObject.SetActive(false)' 형식으로 접근하면 본체 오브젝트 전체를 제어할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) public Slider mySlider; 처럼 하나만 선언해도 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) mySlider.value 로 슬라이더의 값을 바꿀 수 있고, mySlider.gameObject.SetActive(false) 로 슬라이더 오브젝트 자체를 끌 수도 있다. 불필요하게 GameObject형 변수를 따로 만들 필요가 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26. UI 컴포넌트는 하나만 선언해도 본체와 부품을 모두 제어할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) SetActive는 게임오브젝트(본체) 전체의 전원을 끄고 켜는 것이며, enabled는 특정 컴포넌트(부품) 하나만 끄고 켜는 것이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3) 단, 자식클래스는 부모의 '추상 메소드(abstract)'를 무조건 의무적으로 오버라이딩하여 구현해야 한다. (만약 구현을 선택 사항으로 만들고 싶다면 virtual 가상 메소드를 사용해야 한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) 추상클래스를 상속한 자식클래스에서 그 추상메소드를 오버라이딩해서 구현한다. (C#에서는 상속 시 콜론 ':' 기호를 사용한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3) 자식클래스에서 상속하는 경우 반드시 인터페이스의 추상메소드를 의무적으로 구현해줘야 한다. (C#에서는 상속 시 콜론 ':' 기호를 사용한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) SortingLayer로 정렬하기 : Add Sorting Layer -&gt; Layer 추가 (리스트의 아래쪽에 위치한 그룹일수록 화면의 가장 앞에 그려진다) -&gt; 각 오브젝트의 Sorting Layer 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1-1) Order in Layer : 같은 Sorting Layer 안에서는 숫자가 높을수록 앞에 그려진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 클래스는 인스턴스가 Heap 영역에, 구조체는 주로 Stack 영역에 저장된다. (단, 구조체가 클래스 내부의 멤버 필드로 선언된 경우에는 부모 클래스와 함께 Heap 영역에 저장된다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(3) 유니티에서 만드는 방법 : 유니티의 스크립트(MonoBehaviour)는 new 연산자로 생성할 수 없다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>따라서 클래스 내부에 public static 클래스명 instance; 변수를 선언해두고, Awake() 메서드 안에서 if (instance == null) { instance = this; } 와 같이 씬에 존재하는 자기 자신을 할당하는 방식을 사용해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구조체는 값 타입(Value Type)으로 주로 스택(Stack) 메모리에 할당되며, 해당 스코프(메서드 블록 등)를 벗어나면 C# 런타임(CLR)이 스택 프레임을 비우면서 자동으로 메모리가 해제된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) 생성 시점이 아니라, 게임이 실행될 때(Play 버튼 클릭 직후) 또는 Instantiate()를 통해 스크립트가 포함된 오브젝트가 씬에 활성화(생성)되는 순간 최초 1회 호출되는 초기화 메서드. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)리턴값없이 메서드를 종료하는역할 : if문의 바디안에서 메서드를 종료해야할 필요가 있을때 리턴을 써야 메서드가 끝남.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-1) 주의사항 : 유니티에서 뼈대(Bone)는 그 자체로 게임오브젝트이므로, 뼈대의 부자 관계는 하이라키 창의 Transform 부자 관계와 완전히 동일하다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부모 뼈대가 움직이거나 회전(Transform)하면 자식 뼈대의 Transform도 무조건 종속되어 함께 변한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4) GameObject.Find() : (소문자 gameObject가 아니라 대문자 GameObject 클래스의 정적 메서드를 호출해야 함). 씬 전체를 뒤져서 이름으로 게임오브젝트를 찾는다. 단, 비활성 상태인 오브젝트는 찾을 수 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) 배열의 인덱스로 0번(contacts[0])을 주로 쓰는 이유 : 물리 엔진에서는 상자가 바닥에 닿기만 해도 2~4개의 다중 충돌 포인트가 빈번하게 발생한다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여러 개가 생기기 힘들어서가 아니라, 단순히 바닥의 기울기(normal)를 파악할 때는 여러 접점 중 아무 포인트나 딱 1개만 검사해도 충분하기 때문에 편의상 0번 인덱스를 사용하는 것이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 충돌 시 발생하는 모든 접점(Contact Point)들의 정보를 담은 배열.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">/*UI의 위치값을 설정할 때는 가급적 RectTransform형을 꺼내어 사용해야 한다. (추가) 이유: RectTransform은 Transform을 상속받았기 때문에 transform.position을 써도 에러 없이 작동은 한다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">하지만 position(월드 절대 좌표)을 건드리면 화면 해상도가 달라질 때 UI 배치가 다 망가진다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI는 반드시 앵커(Anchor)를 기준으로 움직여야 하므로 RectTransform 고유의 프로퍼티인 anchoredPosition을 사용하는 것이 정석이다. */</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.Renderer 컴포넌트의 머티리얼 접근 방식 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) .material : 원본 보호를 위해 '새로운 복제본(Instance)'을 메모리에 생성하여 반환한다. (개별 오브젝트의 색상만 바꿀 때 사용)</t>
+  </si>
+  <si>
+    <t>(2) .sharedMaterial : 복제 없이 프로젝트 창의 원본 에셋 자체를 건드린다. (이 머티리얼을 사용하는 모든 오브젝트의 색상이 동시에 바뀌므로 주의해서 사용해야 함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4) PlayerPrefs의 보안과 저장 방식 : 플랫폼마다 저장 방식이 다르다. (윈도우는 레지스트리, 안드로이드는 텍스트 기반의 XML 파일). </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안드로이드 기기 루팅 시 텍스트 편집기로 누구나 쉽게 수치를 조작할 수 있으므로, 결제나 재화 같은 중요 데이터는 절대 그냥 저장하면 안 되며 반드시 암호화(Encryption) 처리를 거쳐 서버나 로컬에 저장해야 한다.</t>
+  </si>
+  <si>
+    <t>(1) 기능 : 스크립트상에서 오브젝트의 컴포넌트를 추가해준다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2-1) 최신 표준 사용법(제네릭) : gameObject.AddComponent();</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2) 구식 사용법(비추천) : gameObject.AddComponent(typeof(SphereCollider)); (코드도 길고 타입 캐스팅 과정이 필요해 현재는 잘 쓰지 않음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 게임오브젝트 : 월드 공간의 고유 단위계 (보통 1 Unit = 1미터)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(2) OnClick(PointerClick) : 터치 후 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>버튼 영역 안에서 손을 뗄 때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 실행된다. (만약 버튼을 누른 채로 손가락을 버튼 밖으로 드래그한 뒤 떼면 클릭이 '취소'된다. 모바일 오터치 방지용으로 필수적인 UX 메커니즘)</t>
+    </r>
+  </si>
+  <si>
+    <t>(1) PointerDown : 버튼 영역을 터치(클릭)하는 그 즉시 실행된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mathf.Clamp(float value, float min, float max)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -3442,17 +3534,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3487,7 +3581,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3513,13 +3607,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>476024</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>62802</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3831,13 +3925,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>22861</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>286959</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>30481</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3875,13 +3969,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>297921</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3924,13 +4018,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3984,13 +4078,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -4037,13 +4131,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>118110</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>388620</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -4092,13 +4186,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>534360</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>51900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>38760</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>34320</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
@@ -4157,13 +4251,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>593400</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>9840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>625080</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>46560</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
@@ -4222,13 +4316,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -4331,13 +4425,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>140</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>3054</xdr:colOff>
-      <xdr:row>150</xdr:row>
+      <xdr:row>151</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4375,13 +4469,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>163</xdr:row>
+      <xdr:row>164</xdr:row>
       <xdr:rowOff>205740</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>282541</xdr:colOff>
-      <xdr:row>175</xdr:row>
+      <xdr:row>176</xdr:row>
       <xdr:rowOff>2247</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4424,13 +4518,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>287701</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>14068</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4468,13 +4562,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4534,13 +4628,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>84965</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4578,13 +4672,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4644,13 +4738,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>405231</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4742,13 +4836,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>137160</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>156520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4786,13 +4880,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4856,13 +4950,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4926,13 +5020,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>205740</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4996,13 +5090,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>426720</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5066,13 +5160,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>411480</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>182880</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5136,13 +5230,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>464820</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>205740</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5209,13 +5303,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5279,13 +5373,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>624840</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>434340</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5349,13 +5443,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5419,13 +5513,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>391228</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>3839</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5463,13 +5557,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>30481</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>62641</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5507,13 +5601,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>15804</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>177560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5911,112 +6005,112 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>863</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>855</v>
+        <v>816</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>884</v>
+        <v>840</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>856</v>
+        <v>817</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>857</v>
+        <v>818</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>858</v>
+        <v>819</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6024,80 +6118,80 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>816</v>
+        <v>777</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>749</v>
+        <v>715</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>750</v>
+        <v>716</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>751</v>
+        <v>717</v>
       </c>
       <c r="B41" t="s">
-        <v>752</v>
+        <v>718</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="B42" t="s">
-        <v>728</v>
+        <v>695</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="B43" t="s">
-        <v>753</v>
+        <v>719</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="B44" t="s">
-        <v>754</v>
+        <v>720</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="B45" t="s">
-        <v>732</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -6113,12 +6207,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6128,12 +6222,12 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -6143,47 +6237,47 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>860</v>
+        <v>821</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>815</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>
@@ -6200,27 +6294,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>848</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -6236,32 +6330,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -6271,12 +6365,12 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -6286,7 +6380,7 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -6296,327 +6390,327 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>846</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="B49" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="B50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="B51" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6624,27 +6718,27 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="B94" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -6654,426 +6748,406 @@
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>793</v>
+        <v>757</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>356</v>
+        <v>870</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>871</v>
+        <v>828</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>422</v>
+        <v>866</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>423</v>
+        <v>861</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>872</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>417</v>
+        <v>829</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>419</v>
+        <v>862</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>424</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>431</v>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>451</v>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>673</v>
+        <v>430</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>458</v>
+        <v>641</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>824</v>
+        <v>437</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>10</v>
+        <v>785</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>457</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>513</v>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>520</v>
+        <v>490</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>10</v>
+        <v>491</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>515</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>232</v>
+        <v>494</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>518</v>
+        <v>225</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>516</v>
+        <v>495</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>232</v>
+        <v>496</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>523</v>
+        <v>766</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" t="s">
-        <v>524</v>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>526</v>
+        <v>501</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>527</v>
+        <v>503</v>
       </c>
     </row>
     <row r="183" spans="1:5">
-      <c r="B183" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" t="s">
-        <v>546</v>
+      <c r="A183" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="B184" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="186" spans="1:5">
-      <c r="B186" t="s">
-        <v>548</v>
-      </c>
-      <c r="E186" t="s">
-        <v>550</v>
+      <c r="A186" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="B187" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="E187" t="s">
-        <v>551</v>
+        <v>527</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="B188" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="E188" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" t="s">
-        <v>627</v>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="B189" t="s">
+        <v>526</v>
+      </c>
+      <c r="E189" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>810</v>
+        <v>858</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>811</v>
+        <v>856</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1">
-      <c r="A196" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" t="s">
-        <v>632</v>
+        <v>857</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>680</v>
+        <v>648</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>681</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -7089,22 +7163,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -7115,1050 +7189,1060 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194DBF29-D361-403B-8094-6B4DBAD9B202}">
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>862</v>
+        <v>823</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>846</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>124</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>885</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>819</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>820</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>192</v>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>197</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>211</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>852</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>853</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>212</v>
+        <v>813</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>814</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>490</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>492</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>218</v>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>238</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" t="s">
-        <v>13</v>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" t="s">
-        <v>756</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>469</v>
+        <v>721</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>757</v>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>760</v>
-      </c>
-      <c r="G57" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" t="s">
-        <v>758</v>
+        <v>723</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>3</v>
+        <v>726</v>
+      </c>
+      <c r="G59" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>759</v>
+        <v>724</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>241</v>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>260</v>
+        <v>883</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>255</v>
+        <v>884</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>256</v>
+        <v>891</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>259</v>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>355</v>
+        <v>280</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>354</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>359</v>
+        <v>869</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>383</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>271</v>
+        <v>876</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>272</v>
+        <v>874</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>875</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>262</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>275</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>384</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>369</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>371</v>
+        <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>374</v>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>10</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>381</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>382</v>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>561</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>449</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" t="s">
-        <v>450</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>560</v>
+        <v>537</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="B122" t="s">
-        <v>558</v>
+      <c r="A122" t="s">
+        <v>859</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>562</v>
+        <v>855</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="B124" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" t="s">
-        <v>497</v>
+      <c r="A124" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="B125" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>521</v>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>528</v>
+        <v>485</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>530</v>
+        <v>505</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>532</v>
+        <v>506</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>534</v>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" t="s">
-        <v>556</v>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>554</v>
+        <v>530</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>564</v>
+        <v>531</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>565</v>
+        <v>538</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" t="s">
-        <v>579</v>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>569</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" t="s">
-        <v>472</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>3</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>571</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>577</v>
+        <v>547</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>5</v>
+        <v>552</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>574</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>6</v>
+        <v>549</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>580</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>3</v>
+        <v>555</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>575</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>6</v>
+        <v>550</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>576</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>382</v>
+        <v>551</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>578</v>
+        <v>369</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" t="s">
-        <v>569</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" t="s">
-        <v>472</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>3</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>582</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>5</v>
+        <v>548</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>583</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>6</v>
+        <v>558</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>584</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>3</v>
+        <v>559</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>585</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>6</v>
+        <v>560</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>576</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>382</v>
+        <v>551</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>586</v>
+        <v>369</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" t="s">
-        <v>569</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" t="s">
-        <v>472</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" t="s">
-        <v>3</v>
+        <v>451</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" t="s">
-        <v>588</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" t="s">
-        <v>5</v>
+        <v>548</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" t="s">
-        <v>589</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" t="s">
-        <v>6</v>
+        <v>564</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>590</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>3</v>
+        <v>565</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>591</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>6</v>
+        <v>566</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>576</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1">
-      <c r="A247" t="s">
-        <v>674</v>
+        <v>551</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>675</v>
+        <v>642</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>676</v>
+        <v>643</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>677</v>
+        <v>644</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>678</v>
+        <v>645</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1">
-      <c r="A254" t="s">
-        <v>700</v>
+        <v>646</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" t="s">
-        <v>701</v>
+        <v>668</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1">
-      <c r="A258" t="s">
-        <v>768</v>
+        <v>669</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" t="s">
-        <v>762</v>
+        <v>880</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1">
-      <c r="A262" t="s">
-        <v>763</v>
+        <v>881</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" t="s">
-        <v>764</v>
+        <v>695</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" t="s">
-        <v>765</v>
+        <v>729</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" t="s">
-        <v>766</v>
+        <v>705</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1">
-      <c r="A269" t="s">
-        <v>767</v>
+        <v>730</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" t="s">
         <v>732</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -8175,57 +8259,57 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>842</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>812</v>
+        <v>773</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>841</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>882</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>883</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -8236,252 +8320,257 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5B0EB0-3A18-406B-BDAC-7BBC8487A206}">
-  <dimension ref="A1:A107"/>
+  <dimension ref="A1:A108"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>772</v>
+        <v>737</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>845</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>817</v>
+        <v>778</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>818</v>
+        <v>779</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>393</v>
+        <v>863</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>504</v>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>506</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>621</v>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>623</v>
+        <v>596</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>624</v>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>770</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>773</v>
+        <v>735</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>774</v>
+        <v>738</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>739</v>
       </c>
     </row>
   </sheetData>
@@ -8513,307 +8602,307 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>854</v>
+        <v>815</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>712</v>
+        <v>680</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="K74" t="s">
-        <v>713</v>
+        <v>681</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="K80" t="s">
-        <v>714</v>
+        <v>682</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>783</v>
+        <v>748</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>784</v>
+        <v>749</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>785</v>
+        <v>750</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>786</v>
+        <v>751</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>787</v>
+        <v>752</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>788</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -8830,127 +8919,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>722</v>
+        <v>689</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>723</v>
+        <v>690</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>724</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>725</v>
+        <v>692</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>726</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>727</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>728</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>729</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>730</v>
+        <v>697</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>731</v>
+        <v>698</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>732</v>
+        <v>699</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>733</v>
+        <v>700</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>728</v>
+        <v>695</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>734</v>
+        <v>701</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>735</v>
+        <v>851</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>736</v>
+        <v>702</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>737</v>
+        <v>703</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>738</v>
+        <v>704</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>739</v>
+        <v>705</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>740</v>
+        <v>706</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>741</v>
+        <v>707</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>742</v>
+        <v>708</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>743</v>
+        <v>709</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>744</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>732</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -8961,202 +9050,202 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A67CEF4-BE01-4763-BDC6-975F09EE47AA}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>850</v>
+        <v>811</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>467</v>
+        <v>812</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>465</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>592</v>
+        <v>888</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="H25" t="s">
-        <v>593</v>
+        <v>567</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="H26" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>598</v>
+        <v>568</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="H27" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>600</v>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>601</v>
+        <v>575</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>602</v>
+        <v>576</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>605</v>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>606</v>
+        <v>580</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>607</v>
+        <v>581</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>609</v>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>794</v>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="75" spans="7:7">
-      <c r="G75" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="76" spans="7:7">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="G76" t="s">
-        <v>798</v>
+        <v>761</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="G77" t="s">
+        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -9173,77 +9262,77 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>849</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>864</v>
+        <v>825</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>865</v>
+        <v>826</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>866</v>
+        <v>827</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>682</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>686</v>
+        <v>654</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>683</v>
+        <v>651</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>684</v>
+        <v>652</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>685</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -9259,57 +9348,57 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>879</v>
+        <v>836</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>880</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>
@@ -9325,17 +9414,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>746</v>
+        <v>712</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>747</v>
+        <v>713</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>748</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -9351,82 +9440,82 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>859</v>
+        <v>820</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>844</v>
+        <v>805</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>845</v>
+        <v>806</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -9436,12 +9525,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -9451,197 +9540,197 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>861</v>
+        <v>822</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>873</v>
+        <v>830</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>745</v>
+        <v>711</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>814</v>
+        <v>775</v>
       </c>
     </row>
   </sheetData>
@@ -9652,272 +9741,287 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077E7B44-DC3A-4864-9EC7-4ADF55F1E293}">
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>708</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>874</v>
+        <v>853</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>875</v>
+        <v>854</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>343</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>344</v>
+        <v>832</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>351</v>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>614</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>615</v>
+        <v>588</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>616</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>617</v>
+        <v>590</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>618</v>
+        <v>591</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>619</v>
+        <v>592</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>620</v>
+        <v>593</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>688</v>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>706</v>
+        <v>656</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>707</v>
+        <v>667</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>715</v>
+        <v>674</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>716</v>
+        <v>675</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>717</v>
+        <v>683</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>720</v>
+        <v>684</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>721</v>
+        <v>685</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>718</v>
+        <v>687</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>705</v>
+        <v>688</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>709</v>
+        <v>672</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>711</v>
+        <v>673</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -9937,82 +10041,82 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>689</v>
+        <v>657</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>694</v>
+        <v>662</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>690</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>691</v>
+        <v>659</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>692</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>693</v>
+        <v>661</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>695</v>
+        <v>663</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>696</v>
+        <v>664</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>697</v>
+        <v>665</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>698</v>
+        <v>666</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>804</v>
+        <v>767</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>808</v>
+        <v>771</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>809</v>
+        <v>772</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>805</v>
+        <v>768</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>806</v>
+        <v>769</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>807</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -10024,587 +10128,592 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9A39CD-5B16-41A0-8B36-B999957D39DD}">
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>635</v>
+        <v>604</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>636</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>637</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>638</v>
+        <v>607</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>645</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>639</v>
+        <v>608</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>640</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>641</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>642</v>
+        <v>844</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>813</v>
+        <v>611</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>643</v>
+        <v>774</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>826</v>
+        <v>843</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>827</v>
+        <v>787</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>567</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>829</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>789</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>469</v>
+        <v>790</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>830</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>792</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>832</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>833</v>
+        <v>793</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>794</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>834</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>835</v>
+        <v>795</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>796</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>836</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>838</v>
+        <v>797</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>839</v>
+        <v>799</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>516</v>
+        <v>800</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>840</v>
+        <v>493</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>232</v>
+        <v>801</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>841</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>516</v>
+        <v>802</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>842</v>
+        <v>493</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>843</v>
+        <v>803</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>232</v>
+        <v>804</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>881</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>644</v>
+        <v>838</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>646</v>
+        <v>612</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="B53" t="s">
-        <v>647</v>
+      <c r="A53" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="B54" t="s">
-        <v>469</v>
+        <v>615</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="B55" t="s">
-        <v>472</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="B56" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="B57" t="s">
-        <v>3</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="B58" t="s">
-        <v>825</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="B59" t="s">
-        <v>648</v>
+        <v>786</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="B60" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="B61" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="B62" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="B63" t="s">
-        <v>3</v>
+        <v>617</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="B64" t="s">
-        <v>650</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>651</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>3</v>
+        <v>620</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>653</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>3</v>
+        <v>622</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>655</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="2:6">
       <c r="B81" t="s">
-        <v>10</v>
+        <v>623</v>
       </c>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" t="s">
-        <v>656</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="2:6">
       <c r="B83" t="s">
-        <v>657</v>
+        <v>624</v>
       </c>
     </row>
     <row r="84" spans="2:6">
       <c r="B84" t="s">
-        <v>658</v>
+        <v>625</v>
       </c>
     </row>
     <row r="85" spans="2:6">
       <c r="B85" t="s">
-        <v>657</v>
+        <v>626</v>
       </c>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" t="s">
-        <v>659</v>
+        <v>625</v>
       </c>
     </row>
     <row r="87" spans="2:6">
       <c r="B87" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
     </row>
     <row r="88" spans="2:6">
       <c r="B88" t="s">
-        <v>661</v>
+        <v>628</v>
       </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" t="s">
-        <v>657</v>
+        <v>629</v>
       </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" t="s">
-        <v>13</v>
+        <v>625</v>
       </c>
     </row>
     <row r="91" spans="2:6">
       <c r="B91" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="2:6">
       <c r="B92" t="s">
-        <v>382</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="2:6">
-      <c r="F93" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="F95" t="s">
-        <v>663</v>
+      <c r="B93" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6">
+      <c r="F94" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="F96" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="100" spans="6:6">
-      <c r="F100" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="102" spans="6:6">
-      <c r="F102" t="s">
-        <v>666</v>
+        <v>631</v>
+      </c>
+    </row>
+    <row r="97" spans="6:6">
+      <c r="F97" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="101" spans="6:6">
+      <c r="F101" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="103" spans="6:6">
       <c r="F103" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="105" spans="6:6">
-      <c r="F105" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="109" spans="6:6">
-      <c r="F109" t="s">
-        <v>669</v>
+        <v>634</v>
+      </c>
+    </row>
+    <row r="104" spans="6:6">
+      <c r="F104" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="106" spans="6:6">
+      <c r="F106" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="110" spans="6:6">
       <c r="F110" t="s">
-        <v>670</v>
+        <v>637</v>
       </c>
     </row>
     <row r="111" spans="6:6">
       <c r="F111" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>0</v>
+        <v>638</v>
+      </c>
+    </row>
+    <row r="112" spans="6:6">
+      <c r="F112" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>488</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>5</v>
+        <v>466</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>555</v>
+        <v>603</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>633</v>
+        <v>467</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -10616,7 +10725,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22FACE01-8634-40CF-BA9C-3264EEAD61A5}">
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -10706,97 +10815,97 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10806,7 +10915,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="B41" t="s">
-        <v>539</v>
+        <v>516</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10816,7 +10925,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="B43" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10826,7 +10935,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="B46" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10836,7 +10945,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="B48" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10846,282 +10955,302 @@
     </row>
     <row r="51" spans="1:2">
       <c r="B51" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="B52" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="B53" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>877</v>
+        <v>834</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>878</v>
+        <v>835</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>876</v>
+        <v>833</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>469</v>
+        <v>877</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>471</v>
+        <v>879</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>3</v>
+        <v>448</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>474</v>
+        <v>449</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>477</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>6</v>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>7</v>
+        <v>454</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>3</v>
+        <v>455</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>479</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>480</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="H109" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="H110" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="H114" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="H115" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>802</v>
+        <v>747</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -11138,37 +11267,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>821</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -11184,47 +11313,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>386</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>789</v>
+        <v>754</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>790</v>
+        <v>849</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>792</v>
+        <v>756</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>791</v>
+        <v>755</v>
       </c>
     </row>
   </sheetData>
